--- a/Global/October CMA/Global October CMA Data.xlsx
+++ b/Global/October CMA/Global October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/Global/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C8CC1F-8467-D04E-9B6D-64E1F9F60BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDD2B7D-C4C4-A44C-9DBC-0453DA749751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2818,33 +2818,6 @@
   </cellStyles>
   <dxfs count="31">
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF3F4A58"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FFBB463C"/>
       </font>
@@ -2854,6 +2827,12 @@
           <bgColor rgb="FFFFD9D6"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2875,6 +2854,27 @@
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF3F4A58"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -3206,10 +3206,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Scores" displayName="Scores" ref="A1:AD82">
   <tableColumns count="30">
@@ -3217,9 +3213,9 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Class"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Period" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ELL" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="IEP" dataDxfId="4"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MC"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="CRQ"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Final"/>
@@ -3304,7 +3300,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{37E3D24F-9292-BD43-B3FC-16D6A7D0B3AB}" name="Concatenated" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{37E3D24F-9292-BD43-B3FC-16D6A7D0B3AB}" name="Concatenated" dataDxfId="1">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7344,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="3">
         <f t="shared" si="2"/>
@@ -7635,7 +7631,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="3">
         <f t="shared" si="2"/>
@@ -7829,7 +7825,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="3">
         <f t="shared" si="2"/>
@@ -8116,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="3">
         <f t="shared" si="2"/>
@@ -8504,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="3">
         <f t="shared" si="2"/>
@@ -8698,7 +8694,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="3">
         <f t="shared" si="2"/>
@@ -8892,7 +8888,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="3">
         <f t="shared" si="2"/>
@@ -9177,7 +9173,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" s="3">
         <f t="shared" si="2"/>
@@ -10144,7 +10140,7 @@
         <v>4</v>
       </c>
       <c r="F69" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="10" t="b">
         <v>0</v>
@@ -10341,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="3">
         <f t="shared" si="2"/>
@@ -11016,7 +11012,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="3">
         <f t="shared" si="2"/>
@@ -11307,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="3">
         <f t="shared" si="2"/>
@@ -11404,7 +11400,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="3">
         <f t="shared" si="2"/>
@@ -11481,7 +11477,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:R82">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>W2=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12171,6 +12167,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>

--- a/Global/October CMA/Global October CMA Data.xlsx
+++ b/Global/October CMA/Global October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/Global/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461E92C4-1EBC-F24B-A193-83AF776A77A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8B9E7E-A990-774B-A50E-EBA4C7F0211F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="856">
   <si>
     <t>Model</t>
   </si>
@@ -2420,6 +2420,249 @@
   </si>
   <si>
     <t>Explain the similarity or difference you identified using evidence from both documents.</t>
+  </si>
+  <si>
+    <t>IRV37104</t>
+  </si>
+  <si>
+    <t>JUA27367</t>
+  </si>
+  <si>
+    <t>HMJ88128</t>
+  </si>
+  <si>
+    <t>VIM36434</t>
+  </si>
+  <si>
+    <t>GEY89112</t>
+  </si>
+  <si>
+    <t>XJA95792</t>
+  </si>
+  <si>
+    <t>NPE95670</t>
+  </si>
+  <si>
+    <t>TYB40461</t>
+  </si>
+  <si>
+    <t>KYF53977</t>
+  </si>
+  <si>
+    <t>KOQ20864</t>
+  </si>
+  <si>
+    <t>YJL43166</t>
+  </si>
+  <si>
+    <t>NBB33601</t>
+  </si>
+  <si>
+    <t>PRY28676</t>
+  </si>
+  <si>
+    <t>CUA13132</t>
+  </si>
+  <si>
+    <t>BSC39574</t>
+  </si>
+  <si>
+    <t>WQP13614</t>
+  </si>
+  <si>
+    <t>QZX85356</t>
+  </si>
+  <si>
+    <t>YMW32660</t>
+  </si>
+  <si>
+    <t>JTO50224</t>
+  </si>
+  <si>
+    <t>OYA41269</t>
+  </si>
+  <si>
+    <t>RKB95356</t>
+  </si>
+  <si>
+    <t>ALI86690</t>
+  </si>
+  <si>
+    <t>XZI52182</t>
+  </si>
+  <si>
+    <t>AOJ87475</t>
+  </si>
+  <si>
+    <t>LID92158</t>
+  </si>
+  <si>
+    <t>RNB42487</t>
+  </si>
+  <si>
+    <t>ERI31058</t>
+  </si>
+  <si>
+    <t>RMC48101</t>
+  </si>
+  <si>
+    <t>FHP48293</t>
+  </si>
+  <si>
+    <t>WLU80386</t>
+  </si>
+  <si>
+    <t>MJU44253</t>
+  </si>
+  <si>
+    <t>TWH61493</t>
+  </si>
+  <si>
+    <t>TUD11190</t>
+  </si>
+  <si>
+    <t>BQO32035</t>
+  </si>
+  <si>
+    <t>GZH35654</t>
+  </si>
+  <si>
+    <t>DEH93694</t>
+  </si>
+  <si>
+    <t>ZTS12970</t>
+  </si>
+  <si>
+    <t>SNL78832</t>
+  </si>
+  <si>
+    <t>PAE76784</t>
+  </si>
+  <si>
+    <t>SQT96348</t>
+  </si>
+  <si>
+    <t>PND69183</t>
+  </si>
+  <si>
+    <t>ZTG65553</t>
+  </si>
+  <si>
+    <t>NCC89380</t>
+  </si>
+  <si>
+    <t>OGV62307</t>
+  </si>
+  <si>
+    <t>GGY41496</t>
+  </si>
+  <si>
+    <t>ZRM84184</t>
+  </si>
+  <si>
+    <t>ZVY84429</t>
+  </si>
+  <si>
+    <t>QFF23928</t>
+  </si>
+  <si>
+    <t>ZFI39321</t>
+  </si>
+  <si>
+    <t>SAK32940</t>
+  </si>
+  <si>
+    <t>CCY62645</t>
+  </si>
+  <si>
+    <t>LRD39073</t>
+  </si>
+  <si>
+    <t>ZFW55392</t>
+  </si>
+  <si>
+    <t>ZUZ85484</t>
+  </si>
+  <si>
+    <t>GGF71395</t>
+  </si>
+  <si>
+    <t>BAX29796</t>
+  </si>
+  <si>
+    <t>TWL50281</t>
+  </si>
+  <si>
+    <t>IHP45341</t>
+  </si>
+  <si>
+    <t>QFF13061</t>
+  </si>
+  <si>
+    <t>LND58729</t>
+  </si>
+  <si>
+    <t>OGD80870</t>
+  </si>
+  <si>
+    <t>UCF60506</t>
+  </si>
+  <si>
+    <t>OFB59860</t>
+  </si>
+  <si>
+    <t>PKU98163</t>
+  </si>
+  <si>
+    <t>DJE67758</t>
+  </si>
+  <si>
+    <t>YTD43246</t>
+  </si>
+  <si>
+    <t>AJL10097</t>
+  </si>
+  <si>
+    <t>KKC56827</t>
+  </si>
+  <si>
+    <t>YST56620</t>
+  </si>
+  <si>
+    <t>JDU90102</t>
+  </si>
+  <si>
+    <t>EJI60875</t>
+  </si>
+  <si>
+    <t>ITQ19357</t>
+  </si>
+  <si>
+    <t>IWE28506</t>
+  </si>
+  <si>
+    <t>PCN57081</t>
+  </si>
+  <si>
+    <t>FEN72240</t>
+  </si>
+  <si>
+    <t>JLC23464</t>
+  </si>
+  <si>
+    <t>QFO24091</t>
+  </si>
+  <si>
+    <t>VPT45048</t>
+  </si>
+  <si>
+    <t>WRA67777</t>
+  </si>
+  <si>
+    <t>KAU49795</t>
+  </si>
+  <si>
+    <t>CSC86866</t>
   </si>
 </sst>
 </file>
@@ -2819,53 +3062,23 @@
   <dxfs count="59">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color rgb="FFBB463C"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE8EEF4"/>
+          <fgColor rgb="FFFFD9D6"/>
+          <bgColor rgb="FFFFD9D6"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF5F8FB"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -3847,23 +4060,53 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFBB463C"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFD9D6"/>
-          <bgColor rgb="FFFFD9D6"/>
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF5F8FB"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8EEF4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -4196,57 +4439,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}" name="Scores" displayName="Scores" ref="A1:AB82" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}" name="Scores" displayName="Scores" ref="A1:AB82" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
   <autoFilter ref="A1:AB82" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}"/>
   <tableColumns count="28">
-    <tableColumn id="1" xr3:uid="{BDA62A2B-B3CF-1C42-B26C-859C05903E15}" name="Key" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{B0B24296-AFCF-A649-81B0-797BEB307C4C}" name="Class" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{3E4EABAF-90C9-9E45-B32C-3EE0290EB454}" name="Period" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{C8AD8DDD-6CF2-B44B-9413-E525D4CC5073}" name="ELL" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{D7AFA008-A5EC-0A49-B514-792B12195C8D}" name="IEP" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{B389A40C-5893-DD4D-8A49-52AC9F46E8DC}" name="MC" dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{BDA62A2B-B3CF-1C42-B26C-859C05903E15}" name="Key" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{B0B24296-AFCF-A649-81B0-797BEB307C4C}" name="Class" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{3E4EABAF-90C9-9E45-B32C-3EE0290EB454}" name="Period" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{C8AD8DDD-6CF2-B44B-9413-E525D4CC5073}" name="ELL" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{D7AFA008-A5EC-0A49-B514-792B12195C8D}" name="IEP" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{B389A40C-5893-DD4D-8A49-52AC9F46E8DC}" name="MC" dataDxfId="26">
       <calculatedColumnFormula>SUM(U2:AB2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6D925722-96DA-1749-A527-ACB45D97657F}" name="CRQ" dataDxfId="23">
+    <tableColumn id="7" xr3:uid="{6D925722-96DA-1749-A527-ACB45D97657F}" name="CRQ" dataDxfId="25">
       <calculatedColumnFormula>SUM(Q2:T2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D6CC8E81-E712-E74D-B287-58B154A14A59}" name="Final" dataDxfId="22">
+    <tableColumn id="8" xr3:uid="{D6CC8E81-E712-E74D-B287-58B154A14A59}" name="Final" dataDxfId="24">
       <calculatedColumnFormula>SUM(F2:G2)/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D1D28B64-20BB-A248-9F60-F9562825ED9A}" name="1" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{DD495C25-BB33-2345-91D2-F162C405127D}" name="2" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{877B2BEA-ABD1-4141-9BCB-AE69EC7CD0E1}" name="3" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{E3553FF6-A35E-F24D-8F9B-FDFF853CA939}" name="4" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{F53C2052-E00C-5D47-94E2-6EEAA85E072A}" name="5" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{35F06D73-5AA1-6B40-9E5F-B9B979ED3AEF}" name="6" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{39F41D5F-D329-AA46-8E9E-8ADB32807EA2}" name="7" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{C1B096E8-3D38-8940-97B2-71D100A0AEFE}" name="8" dataDxfId="14"/>
-    <tableColumn id="17" xr3:uid="{939E4559-1632-1F41-9C13-FEDC9442CD17}" name="9" dataDxfId="13"/>
-    <tableColumn id="18" xr3:uid="{76B6A234-B47B-5648-88B2-B69A0A91AA7F}" name="10" dataDxfId="12"/>
-    <tableColumn id="19" xr3:uid="{4572F0CE-AA1A-FA40-B8BC-8D9A1BE127FD}" name="11a" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{E57F7912-B3EE-6546-A077-CCEDE62E69CB}" name="11b" dataDxfId="10"/>
-    <tableColumn id="21" xr3:uid="{BE7F2F6D-BF60-B946-A037-26D6B1B11F6E}" name="Q1" dataDxfId="9">
+    <tableColumn id="9" xr3:uid="{D1D28B64-20BB-A248-9F60-F9562825ED9A}" name="1" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{DD495C25-BB33-2345-91D2-F162C405127D}" name="2" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{877B2BEA-ABD1-4141-9BCB-AE69EC7CD0E1}" name="3" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{E3553FF6-A35E-F24D-8F9B-FDFF853CA939}" name="4" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{F53C2052-E00C-5D47-94E2-6EEAA85E072A}" name="5" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{35F06D73-5AA1-6B40-9E5F-B9B979ED3AEF}" name="6" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{39F41D5F-D329-AA46-8E9E-8ADB32807EA2}" name="7" dataDxfId="17"/>
+    <tableColumn id="16" xr3:uid="{C1B096E8-3D38-8940-97B2-71D100A0AEFE}" name="8" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{939E4559-1632-1F41-9C13-FEDC9442CD17}" name="9" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{76B6A234-B47B-5648-88B2-B69A0A91AA7F}" name="10" dataDxfId="14"/>
+    <tableColumn id="19" xr3:uid="{4572F0CE-AA1A-FA40-B8BC-8D9A1BE127FD}" name="11a" dataDxfId="13"/>
+    <tableColumn id="20" xr3:uid="{E57F7912-B3EE-6546-A077-CCEDE62E69CB}" name="11b" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{BE7F2F6D-BF60-B946-A037-26D6B1B11F6E}" name="Q1" dataDxfId="11">
       <calculatedColumnFormula>IF(I2=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{063CA0F4-6645-C64D-83B7-DC255660A115}" name="Q2" dataDxfId="8">
+    <tableColumn id="22" xr3:uid="{063CA0F4-6645-C64D-83B7-DC255660A115}" name="Q2" dataDxfId="10">
       <calculatedColumnFormula>IF(J2=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D9FF7CCF-E3CE-E346-BDFA-80BAB418F49E}" name="Q3" dataDxfId="7">
+    <tableColumn id="23" xr3:uid="{D9FF7CCF-E3CE-E346-BDFA-80BAB418F49E}" name="Q3" dataDxfId="9">
       <calculatedColumnFormula>IF(K2=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{09C89755-22BC-4447-9D0A-0863BC742B45}" name="Q4" dataDxfId="6">
+    <tableColumn id="24" xr3:uid="{09C89755-22BC-4447-9D0A-0863BC742B45}" name="Q4" dataDxfId="8">
       <calculatedColumnFormula>IF(L2=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{BE88876E-C474-3643-A5CC-00B7AD3AA5C8}" name="Q5" dataDxfId="5">
+    <tableColumn id="25" xr3:uid="{BE88876E-C474-3643-A5CC-00B7AD3AA5C8}" name="Q5" dataDxfId="7">
       <calculatedColumnFormula>IF(M2=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{2DCEBFD7-23EB-8042-A4B6-1DE27B9DBEEB}" name="Q6" dataDxfId="4">
+    <tableColumn id="26" xr3:uid="{2DCEBFD7-23EB-8042-A4B6-1DE27B9DBEEB}" name="Q6" dataDxfId="6">
       <calculatedColumnFormula>IF(N2=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6279084C-A701-514B-80D0-60A3AC2988F8}" name="Q7" dataDxfId="3">
+    <tableColumn id="27" xr3:uid="{6279084C-A701-514B-80D0-60A3AC2988F8}" name="Q7" dataDxfId="5">
       <calculatedColumnFormula>IF(O2=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{9F80D501-AEF1-0045-854D-12FF8420DBD3}" name="Q8" dataDxfId="2">
+    <tableColumn id="28" xr3:uid="{9F80D501-AEF1-0045-854D-12FF8420DBD3}" name="Q8" dataDxfId="4">
       <calculatedColumnFormula>IF(P2=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4272,10 +4515,10 @@
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="34">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="3">
       <calculatedColumnFormula>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="33">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="2">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4310,7 +4553,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{37E3D24F-9292-BD43-B3FC-16D6A7D0B3AB}" name="Concatenated" dataDxfId="32">
+    <tableColumn id="4" xr3:uid="{37E3D24F-9292-BD43-B3FC-16D6A7D0B3AB}" name="Concatenated" dataDxfId="1">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4639,8 +4882,8 @@
       </c>
     </row>
     <row r="2" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="10">
-        <v>1</v>
+      <c r="A2" s="10" t="s">
+        <v>775</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>69</v>
@@ -4728,8 +4971,8 @@
       </c>
     </row>
     <row r="3" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10">
-        <v>2</v>
+      <c r="A3" s="10" t="s">
+        <v>776</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>69</v>
@@ -4817,8 +5060,8 @@
       </c>
     </row>
     <row r="4" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10">
-        <v>3</v>
+      <c r="A4" s="10" t="s">
+        <v>777</v>
       </c>
       <c r="B4" s="28" t="s">
         <v>69</v>
@@ -4906,8 +5149,8 @@
       </c>
     </row>
     <row r="5" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10">
-        <v>4</v>
+      <c r="A5" s="10" t="s">
+        <v>778</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>69</v>
@@ -4995,8 +5238,8 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10">
-        <v>5</v>
+      <c r="A6" s="10" t="s">
+        <v>779</v>
       </c>
       <c r="B6" s="28" t="s">
         <v>69</v>
@@ -5084,8 +5327,8 @@
       </c>
     </row>
     <row r="7" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10">
-        <v>6</v>
+      <c r="A7" s="10" t="s">
+        <v>780</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>69</v>
@@ -5171,8 +5414,8 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10">
-        <v>7</v>
+      <c r="A8" s="10" t="s">
+        <v>781</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>69</v>
@@ -5260,8 +5503,8 @@
       </c>
     </row>
     <row r="9" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10">
-        <v>8</v>
+      <c r="A9" s="10" t="s">
+        <v>782</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>69</v>
@@ -5349,8 +5592,8 @@
       </c>
     </row>
     <row r="10" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10">
-        <v>9</v>
+      <c r="A10" s="10" t="s">
+        <v>783</v>
       </c>
       <c r="B10" s="28" t="s">
         <v>69</v>
@@ -5438,8 +5681,8 @@
       </c>
     </row>
     <row r="11" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10">
-        <v>10</v>
+      <c r="A11" s="10" t="s">
+        <v>784</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>69</v>
@@ -5527,8 +5770,8 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="10">
-        <v>11</v>
+      <c r="A12" s="10" t="s">
+        <v>785</v>
       </c>
       <c r="B12" s="28" t="s">
         <v>69</v>
@@ -5616,8 +5859,8 @@
       </c>
     </row>
     <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="10">
-        <v>12</v>
+      <c r="A13" s="10" t="s">
+        <v>786</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>69</v>
@@ -5705,8 +5948,8 @@
       </c>
     </row>
     <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="10">
-        <v>13</v>
+      <c r="A14" s="10" t="s">
+        <v>787</v>
       </c>
       <c r="B14" s="28" t="s">
         <v>69</v>
@@ -5794,8 +6037,8 @@
       </c>
     </row>
     <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="10">
-        <v>14</v>
+      <c r="A15" s="10" t="s">
+        <v>788</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>69</v>
@@ -5883,8 +6126,8 @@
       </c>
     </row>
     <row r="16" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="10">
-        <v>15</v>
+      <c r="A16" s="10" t="s">
+        <v>789</v>
       </c>
       <c r="B16" s="28" t="s">
         <v>69</v>
@@ -5972,8 +6215,8 @@
       </c>
     </row>
     <row r="17" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="10">
-        <v>16</v>
+      <c r="A17" s="10" t="s">
+        <v>790</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>69</v>
@@ -6061,8 +6304,8 @@
       </c>
     </row>
     <row r="18" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="10">
-        <v>17</v>
+      <c r="A18" s="10" t="s">
+        <v>791</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>69</v>
@@ -6150,8 +6393,8 @@
       </c>
     </row>
     <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="10">
-        <v>18</v>
+      <c r="A19" s="10" t="s">
+        <v>792</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>69</v>
@@ -6239,8 +6482,8 @@
       </c>
     </row>
     <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="10">
-        <v>19</v>
+      <c r="A20" s="10" t="s">
+        <v>793</v>
       </c>
       <c r="B20" s="28" t="s">
         <v>69</v>
@@ -6328,8 +6571,8 @@
       </c>
     </row>
     <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="10">
-        <v>20</v>
+      <c r="A21" s="10" t="s">
+        <v>794</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>69</v>
@@ -6417,8 +6660,8 @@
       </c>
     </row>
     <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="10">
-        <v>21</v>
+      <c r="A22" s="10" t="s">
+        <v>795</v>
       </c>
       <c r="B22" s="28" t="s">
         <v>69</v>
@@ -6506,8 +6749,8 @@
       </c>
     </row>
     <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="10">
-        <v>22</v>
+      <c r="A23" s="10" t="s">
+        <v>796</v>
       </c>
       <c r="B23" s="22" t="s">
         <v>69</v>
@@ -6595,8 +6838,8 @@
       </c>
     </row>
     <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="10">
-        <v>23</v>
+      <c r="A24" s="10" t="s">
+        <v>797</v>
       </c>
       <c r="B24" s="28" t="s">
         <v>69</v>
@@ -6684,8 +6927,8 @@
       </c>
     </row>
     <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="10">
-        <v>24</v>
+      <c r="A25" s="10" t="s">
+        <v>798</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>69</v>
@@ -6773,8 +7016,8 @@
       </c>
     </row>
     <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="10">
-        <v>25</v>
+      <c r="A26" s="10" t="s">
+        <v>799</v>
       </c>
       <c r="B26" s="28" t="s">
         <v>69</v>
@@ -6862,8 +7105,8 @@
       </c>
     </row>
     <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="10">
-        <v>26</v>
+      <c r="A27" s="10" t="s">
+        <v>800</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>69</v>
@@ -6951,8 +7194,8 @@
       </c>
     </row>
     <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="10">
-        <v>27</v>
+      <c r="A28" s="10" t="s">
+        <v>801</v>
       </c>
       <c r="B28" s="28" t="s">
         <v>69</v>
@@ -7040,8 +7283,8 @@
       </c>
     </row>
     <row r="29" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="10">
-        <v>28</v>
+      <c r="A29" s="10" t="s">
+        <v>802</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>69</v>
@@ -7129,8 +7372,8 @@
       </c>
     </row>
     <row r="30" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="10">
-        <v>29</v>
+      <c r="A30" s="10" t="s">
+        <v>803</v>
       </c>
       <c r="B30" s="28" t="s">
         <v>69</v>
@@ -7218,8 +7461,8 @@
       </c>
     </row>
     <row r="31" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10">
-        <v>30</v>
+      <c r="A31" s="10" t="s">
+        <v>804</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>69</v>
@@ -7307,8 +7550,8 @@
       </c>
     </row>
     <row r="32" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10">
-        <v>31</v>
+      <c r="A32" s="10" t="s">
+        <v>805</v>
       </c>
       <c r="B32" s="28" t="s">
         <v>69</v>
@@ -7396,8 +7639,8 @@
       </c>
     </row>
     <row r="33" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="10">
-        <v>32</v>
+      <c r="A33" s="10" t="s">
+        <v>806</v>
       </c>
       <c r="B33" s="22" t="s">
         <v>69</v>
@@ -7485,8 +7728,8 @@
       </c>
     </row>
     <row r="34" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="10">
-        <v>33</v>
+      <c r="A34" s="10" t="s">
+        <v>807</v>
       </c>
       <c r="B34" s="28" t="s">
         <v>69</v>
@@ -7574,8 +7817,8 @@
       </c>
     </row>
     <row r="35" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="10">
-        <v>34</v>
+      <c r="A35" s="10" t="s">
+        <v>808</v>
       </c>
       <c r="B35" s="22" t="s">
         <v>69</v>
@@ -7663,8 +7906,8 @@
       </c>
     </row>
     <row r="36" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="10">
-        <v>35</v>
+      <c r="A36" s="10" t="s">
+        <v>809</v>
       </c>
       <c r="B36" s="28" t="s">
         <v>69</v>
@@ -7752,8 +7995,8 @@
       </c>
     </row>
     <row r="37" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="10">
-        <v>36</v>
+      <c r="A37" s="10" t="s">
+        <v>810</v>
       </c>
       <c r="B37" s="22" t="s">
         <v>69</v>
@@ -7841,8 +8084,8 @@
       </c>
     </row>
     <row r="38" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="10">
-        <v>37</v>
+      <c r="A38" s="10" t="s">
+        <v>811</v>
       </c>
       <c r="B38" s="28" t="s">
         <v>69</v>
@@ -7930,8 +8173,8 @@
       </c>
     </row>
     <row r="39" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="10">
-        <v>38</v>
+      <c r="A39" s="10" t="s">
+        <v>812</v>
       </c>
       <c r="B39" s="22" t="s">
         <v>69</v>
@@ -8019,8 +8262,8 @@
       </c>
     </row>
     <row r="40" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="10">
-        <v>39</v>
+      <c r="A40" s="10" t="s">
+        <v>813</v>
       </c>
       <c r="B40" s="28" t="s">
         <v>46</v>
@@ -8108,8 +8351,8 @@
       </c>
     </row>
     <row r="41" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="10">
-        <v>40</v>
+      <c r="A41" s="10" t="s">
+        <v>814</v>
       </c>
       <c r="B41" s="22" t="s">
         <v>46</v>
@@ -8197,8 +8440,8 @@
       </c>
     </row>
     <row r="42" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="10">
-        <v>41</v>
+      <c r="A42" s="10" t="s">
+        <v>815</v>
       </c>
       <c r="B42" s="28" t="s">
         <v>46</v>
@@ -8286,8 +8529,8 @@
       </c>
     </row>
     <row r="43" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="10">
-        <v>42</v>
+      <c r="A43" s="10" t="s">
+        <v>816</v>
       </c>
       <c r="B43" s="22" t="s">
         <v>46</v>
@@ -8375,8 +8618,8 @@
       </c>
     </row>
     <row r="44" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="10">
-        <v>43</v>
+      <c r="A44" s="10" t="s">
+        <v>817</v>
       </c>
       <c r="B44" s="28" t="s">
         <v>46</v>
@@ -8464,8 +8707,8 @@
       </c>
     </row>
     <row r="45" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="10">
-        <v>44</v>
+      <c r="A45" s="10" t="s">
+        <v>818</v>
       </c>
       <c r="B45" s="22" t="s">
         <v>46</v>
@@ -8553,8 +8796,8 @@
       </c>
     </row>
     <row r="46" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="10">
-        <v>45</v>
+      <c r="A46" s="10" t="s">
+        <v>819</v>
       </c>
       <c r="B46" s="28" t="s">
         <v>46</v>
@@ -8638,8 +8881,8 @@
       </c>
     </row>
     <row r="47" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="10">
-        <v>46</v>
+      <c r="A47" s="10" t="s">
+        <v>820</v>
       </c>
       <c r="B47" s="22" t="s">
         <v>46</v>
@@ -8727,8 +8970,8 @@
       </c>
     </row>
     <row r="48" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="10">
-        <v>47</v>
+      <c r="A48" s="10" t="s">
+        <v>821</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>46</v>
@@ -8816,8 +9059,8 @@
       </c>
     </row>
     <row r="49" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="10">
-        <v>48</v>
+      <c r="A49" s="10" t="s">
+        <v>822</v>
       </c>
       <c r="B49" s="22" t="s">
         <v>46</v>
@@ -8905,8 +9148,8 @@
       </c>
     </row>
     <row r="50" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="10">
-        <v>49</v>
+      <c r="A50" s="10" t="s">
+        <v>823</v>
       </c>
       <c r="B50" s="28" t="s">
         <v>46</v>
@@ -8994,8 +9237,8 @@
       </c>
     </row>
     <row r="51" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="10">
-        <v>50</v>
+      <c r="A51" s="10" t="s">
+        <v>824</v>
       </c>
       <c r="B51" s="22" t="s">
         <v>46</v>
@@ -9083,8 +9326,8 @@
       </c>
     </row>
     <row r="52" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="10">
-        <v>51</v>
+      <c r="A52" s="10" t="s">
+        <v>825</v>
       </c>
       <c r="B52" s="28" t="s">
         <v>46</v>
@@ -9172,8 +9415,8 @@
       </c>
     </row>
     <row r="53" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="10">
-        <v>52</v>
+      <c r="A53" s="10" t="s">
+        <v>826</v>
       </c>
       <c r="B53" s="22" t="s">
         <v>46</v>
@@ -9261,8 +9504,8 @@
       </c>
     </row>
     <row r="54" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="10">
-        <v>53</v>
+      <c r="A54" s="10" t="s">
+        <v>827</v>
       </c>
       <c r="B54" s="28" t="s">
         <v>46</v>
@@ -9350,8 +9593,8 @@
       </c>
     </row>
     <row r="55" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="10">
-        <v>54</v>
+      <c r="A55" s="10" t="s">
+        <v>828</v>
       </c>
       <c r="B55" s="22" t="s">
         <v>46</v>
@@ -9439,8 +9682,8 @@
       </c>
     </row>
     <row r="56" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="10">
-        <v>55</v>
+      <c r="A56" s="10" t="s">
+        <v>829</v>
       </c>
       <c r="B56" s="28" t="s">
         <v>46</v>
@@ -9528,8 +9771,8 @@
       </c>
     </row>
     <row r="57" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="10">
-        <v>56</v>
+      <c r="A57" s="10" t="s">
+        <v>830</v>
       </c>
       <c r="B57" s="22" t="s">
         <v>46</v>
@@ -9611,8 +9854,8 @@
       </c>
     </row>
     <row r="58" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="10">
-        <v>57</v>
+      <c r="A58" s="10" t="s">
+        <v>831</v>
       </c>
       <c r="B58" s="28" t="s">
         <v>46</v>
@@ -9700,8 +9943,8 @@
       </c>
     </row>
     <row r="59" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="10">
-        <v>58</v>
+      <c r="A59" s="10" t="s">
+        <v>832</v>
       </c>
       <c r="B59" s="22" t="s">
         <v>46</v>
@@ -9789,8 +10032,8 @@
       </c>
     </row>
     <row r="60" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="10">
-        <v>59</v>
+      <c r="A60" s="10" t="s">
+        <v>833</v>
       </c>
       <c r="B60" s="28" t="s">
         <v>46</v>
@@ -9878,8 +10121,8 @@
       </c>
     </row>
     <row r="61" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="10">
-        <v>60</v>
+      <c r="A61" s="10" t="s">
+        <v>834</v>
       </c>
       <c r="B61" s="22" t="s">
         <v>46</v>
@@ -9967,8 +10210,8 @@
       </c>
     </row>
     <row r="62" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="10">
-        <v>61</v>
+      <c r="A62" s="10" t="s">
+        <v>835</v>
       </c>
       <c r="B62" s="28" t="s">
         <v>46</v>
@@ -10056,8 +10299,8 @@
       </c>
     </row>
     <row r="63" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="10">
-        <v>62</v>
+      <c r="A63" s="10" t="s">
+        <v>836</v>
       </c>
       <c r="B63" s="22" t="s">
         <v>46</v>
@@ -10145,8 +10388,8 @@
       </c>
     </row>
     <row r="64" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="10">
-        <v>63</v>
+      <c r="A64" s="10" t="s">
+        <v>837</v>
       </c>
       <c r="B64" s="28" t="s">
         <v>46</v>
@@ -10234,8 +10477,8 @@
       </c>
     </row>
     <row r="65" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="10">
-        <v>64</v>
+      <c r="A65" s="10" t="s">
+        <v>838</v>
       </c>
       <c r="B65" s="22" t="s">
         <v>46</v>
@@ -10323,8 +10566,8 @@
       </c>
     </row>
     <row r="66" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="10">
-        <v>65</v>
+      <c r="A66" s="10" t="s">
+        <v>839</v>
       </c>
       <c r="B66" s="28" t="s">
         <v>46</v>
@@ -10412,8 +10655,8 @@
       </c>
     </row>
     <row r="67" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="10">
-        <v>66</v>
+      <c r="A67" s="10" t="s">
+        <v>840</v>
       </c>
       <c r="B67" s="22" t="s">
         <v>46</v>
@@ -10501,8 +10744,8 @@
       </c>
     </row>
     <row r="68" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="10">
-        <v>67</v>
+      <c r="A68" s="10" t="s">
+        <v>841</v>
       </c>
       <c r="B68" s="28" t="s">
         <v>46</v>
@@ -10590,8 +10833,8 @@
       </c>
     </row>
     <row r="69" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="10">
-        <v>68</v>
+      <c r="A69" s="10" t="s">
+        <v>842</v>
       </c>
       <c r="B69" s="22" t="s">
         <v>46</v>
@@ -10679,8 +10922,8 @@
       </c>
     </row>
     <row r="70" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="10">
-        <v>69</v>
+      <c r="A70" s="10" t="s">
+        <v>843</v>
       </c>
       <c r="B70" s="28" t="s">
         <v>46</v>
@@ -10768,8 +11011,8 @@
       </c>
     </row>
     <row r="71" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="10">
-        <v>70</v>
+      <c r="A71" s="10" t="s">
+        <v>844</v>
       </c>
       <c r="B71" s="22" t="s">
         <v>46</v>
@@ -10857,8 +11100,8 @@
       </c>
     </row>
     <row r="72" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="10">
-        <v>71</v>
+      <c r="A72" s="10" t="s">
+        <v>845</v>
       </c>
       <c r="B72" s="28" t="s">
         <v>46</v>
@@ -10946,8 +11189,8 @@
       </c>
     </row>
     <row r="73" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="10">
-        <v>72</v>
+      <c r="A73" s="10" t="s">
+        <v>846</v>
       </c>
       <c r="B73" s="22" t="s">
         <v>46</v>
@@ -11035,8 +11278,8 @@
       </c>
     </row>
     <row r="74" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="10">
-        <v>73</v>
+      <c r="A74" s="10" t="s">
+        <v>847</v>
       </c>
       <c r="B74" s="28" t="s">
         <v>46</v>
@@ -11124,8 +11367,8 @@
       </c>
     </row>
     <row r="75" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="10">
-        <v>74</v>
+      <c r="A75" s="10" t="s">
+        <v>848</v>
       </c>
       <c r="B75" s="22" t="s">
         <v>46</v>
@@ -11213,8 +11456,8 @@
       </c>
     </row>
     <row r="76" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="10">
-        <v>75</v>
+      <c r="A76" s="10" t="s">
+        <v>849</v>
       </c>
       <c r="B76" s="28" t="s">
         <v>46</v>
@@ -11298,8 +11541,8 @@
       </c>
     </row>
     <row r="77" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="10">
-        <v>76</v>
+      <c r="A77" s="10" t="s">
+        <v>850</v>
       </c>
       <c r="B77" s="22" t="s">
         <v>46</v>
@@ -11387,8 +11630,8 @@
       </c>
     </row>
     <row r="78" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="10">
-        <v>77</v>
+      <c r="A78" s="10" t="s">
+        <v>851</v>
       </c>
       <c r="B78" s="28" t="s">
         <v>46</v>
@@ -11476,8 +11719,8 @@
       </c>
     </row>
     <row r="79" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="10">
-        <v>78</v>
+      <c r="A79" s="10" t="s">
+        <v>852</v>
       </c>
       <c r="B79" s="22" t="s">
         <v>46</v>
@@ -11565,8 +11808,8 @@
       </c>
     </row>
     <row r="80" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="10">
-        <v>79</v>
+      <c r="A80" s="10" t="s">
+        <v>853</v>
       </c>
       <c r="B80" s="28" t="s">
         <v>46</v>
@@ -11654,8 +11897,8 @@
       </c>
     </row>
     <row r="81" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="10">
-        <v>80</v>
+      <c r="A81" s="10" t="s">
+        <v>854</v>
       </c>
       <c r="B81" s="22" t="s">
         <v>46</v>
@@ -11743,8 +11986,8 @@
       </c>
     </row>
     <row r="82" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="10">
-        <v>81</v>
+      <c r="A82" s="10" t="s">
+        <v>855</v>
       </c>
       <c r="B82" s="34" t="s">
         <v>46</v>
@@ -11833,7 +12076,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:P82">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>U2=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Global/October CMA/Global October CMA Data.xlsx
+++ b/Global/October CMA/Global October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/Global/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8B9E7E-A990-774B-A50E-EBA4C7F0211F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90155225-EC9E-104E-89E3-1CA6AF2558E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Global/October CMA/Global October CMA Data.xlsx
+++ b/Global/October CMA/Global October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/Global/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90155225-EC9E-104E-89E3-1CA6AF2558E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309707F9-1A71-894C-A93D-A1887A033B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="857">
   <si>
     <t>Model</t>
   </si>
@@ -2663,6 +2663,9 @@
   </si>
   <si>
     <t>CSC86866</t>
+  </si>
+  <si>
+    <t>FAL91039</t>
   </si>
 </sst>
 </file>
@@ -3059,7 +3062,18 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{E24C90E3-2734-B149-B611-0E6AC5E040E3}"/>
   </cellStyles>
-  <dxfs count="59">
+  <dxfs count="60">
+    <dxf>
+      <font>
+        <color rgb="FFBB463C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFD9D6"/>
+          <bgColor rgb="FFFFD9D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFBB463C"/>
@@ -4369,40 +4383,40 @@
   </dxfs>
   <tableStyles count="6">
     <tableStyle name="Questions-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="58"/>
-      <tableStyleElement type="headerRow" dxfId="57"/>
-      <tableStyleElement type="firstRowStripe" dxfId="56"/>
-      <tableStyleElement type="secondRowStripe" dxfId="55"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="59"/>
+      <tableStyleElement type="headerRow" dxfId="58"/>
+      <tableStyleElement type="firstRowStripe" dxfId="57"/>
+      <tableStyleElement type="secondRowStripe" dxfId="56"/>
     </tableStyle>
     <tableStyle name="Task Models-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="54"/>
-      <tableStyleElement type="headerRow" dxfId="53"/>
-      <tableStyleElement type="firstRowStripe" dxfId="52"/>
-      <tableStyleElement type="secondRowStripe" dxfId="51"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="55"/>
+      <tableStyleElement type="headerRow" dxfId="54"/>
+      <tableStyleElement type="firstRowStripe" dxfId="53"/>
+      <tableStyleElement type="secondRowStripe" dxfId="52"/>
     </tableStyle>
     <tableStyle name="Scores-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="50"/>
-      <tableStyleElement type="headerRow" dxfId="49"/>
-      <tableStyleElement type="firstRowStripe" dxfId="48"/>
-      <tableStyleElement type="secondRowStripe" dxfId="47"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="51"/>
+      <tableStyleElement type="headerRow" dxfId="50"/>
+      <tableStyleElement type="firstRowStripe" dxfId="49"/>
+      <tableStyleElement type="secondRowStripe" dxfId="48"/>
     </tableStyle>
     <tableStyle name="Skill Standards-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="46"/>
-      <tableStyleElement type="headerRow" dxfId="45"/>
-      <tableStyleElement type="firstRowStripe" dxfId="44"/>
-      <tableStyleElement type="secondRowStripe" dxfId="43"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="47"/>
+      <tableStyleElement type="headerRow" dxfId="46"/>
+      <tableStyleElement type="firstRowStripe" dxfId="45"/>
+      <tableStyleElement type="secondRowStripe" dxfId="44"/>
     </tableStyle>
     <tableStyle name="Content Standards-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="42"/>
-      <tableStyleElement type="headerRow" dxfId="41"/>
-      <tableStyleElement type="firstRowStripe" dxfId="40"/>
-      <tableStyleElement type="secondRowStripe" dxfId="39"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="43"/>
+      <tableStyleElement type="headerRow" dxfId="42"/>
+      <tableStyleElement type="firstRowStripe" dxfId="41"/>
+      <tableStyleElement type="secondRowStripe" dxfId="40"/>
     </tableStyle>
     <tableStyle name="Light and Airy" count="4" xr9:uid="{D3C6459B-EC7F-4F41-B005-22E80AE40871}">
-      <tableStyleElement type="wholeTable" dxfId="38"/>
-      <tableStyleElement type="headerRow" dxfId="37"/>
-      <tableStyleElement type="totalRow" dxfId="36"/>
-      <tableStyleElement type="firstRowStripe" dxfId="35"/>
+      <tableStyleElement type="wholeTable" dxfId="39"/>
+      <tableStyleElement type="headerRow" dxfId="38"/>
+      <tableStyleElement type="totalRow" dxfId="37"/>
+      <tableStyleElement type="firstRowStripe" dxfId="36"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4439,57 +4453,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}" name="Scores" displayName="Scores" ref="A1:AB82" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
-  <autoFilter ref="A1:AB82" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}" name="Scores" displayName="Scores" ref="A1:AB83" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" tableBorderDxfId="33">
+  <autoFilter ref="A1:AB83" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}"/>
   <tableColumns count="28">
-    <tableColumn id="1" xr3:uid="{BDA62A2B-B3CF-1C42-B26C-859C05903E15}" name="Key" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{B0B24296-AFCF-A649-81B0-797BEB307C4C}" name="Class" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{3E4EABAF-90C9-9E45-B32C-3EE0290EB454}" name="Period" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{C8AD8DDD-6CF2-B44B-9413-E525D4CC5073}" name="ELL" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{D7AFA008-A5EC-0A49-B514-792B12195C8D}" name="IEP" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{B389A40C-5893-DD4D-8A49-52AC9F46E8DC}" name="MC" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{BDA62A2B-B3CF-1C42-B26C-859C05903E15}" name="Key" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{B0B24296-AFCF-A649-81B0-797BEB307C4C}" name="Class" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{3E4EABAF-90C9-9E45-B32C-3EE0290EB454}" name="Period" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{C8AD8DDD-6CF2-B44B-9413-E525D4CC5073}" name="ELL" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{D7AFA008-A5EC-0A49-B514-792B12195C8D}" name="IEP" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{B389A40C-5893-DD4D-8A49-52AC9F46E8DC}" name="MC" dataDxfId="27">
       <calculatedColumnFormula>SUM(U2:AB2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6D925722-96DA-1749-A527-ACB45D97657F}" name="CRQ" dataDxfId="25">
+    <tableColumn id="7" xr3:uid="{6D925722-96DA-1749-A527-ACB45D97657F}" name="CRQ" dataDxfId="26">
       <calculatedColumnFormula>SUM(Q2:T2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D6CC8E81-E712-E74D-B287-58B154A14A59}" name="Final" dataDxfId="24">
+    <tableColumn id="8" xr3:uid="{D6CC8E81-E712-E74D-B287-58B154A14A59}" name="Final" dataDxfId="25">
       <calculatedColumnFormula>SUM(F2:G2)/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D1D28B64-20BB-A248-9F60-F9562825ED9A}" name="1" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{DD495C25-BB33-2345-91D2-F162C405127D}" name="2" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{877B2BEA-ABD1-4141-9BCB-AE69EC7CD0E1}" name="3" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{E3553FF6-A35E-F24D-8F9B-FDFF853CA939}" name="4" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{F53C2052-E00C-5D47-94E2-6EEAA85E072A}" name="5" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{35F06D73-5AA1-6B40-9E5F-B9B979ED3AEF}" name="6" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{39F41D5F-D329-AA46-8E9E-8ADB32807EA2}" name="7" dataDxfId="17"/>
-    <tableColumn id="16" xr3:uid="{C1B096E8-3D38-8940-97B2-71D100A0AEFE}" name="8" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{939E4559-1632-1F41-9C13-FEDC9442CD17}" name="9" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{76B6A234-B47B-5648-88B2-B69A0A91AA7F}" name="10" dataDxfId="14"/>
-    <tableColumn id="19" xr3:uid="{4572F0CE-AA1A-FA40-B8BC-8D9A1BE127FD}" name="11a" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{E57F7912-B3EE-6546-A077-CCEDE62E69CB}" name="11b" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{BE7F2F6D-BF60-B946-A037-26D6B1B11F6E}" name="Q1" dataDxfId="11">
+    <tableColumn id="9" xr3:uid="{D1D28B64-20BB-A248-9F60-F9562825ED9A}" name="1" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{DD495C25-BB33-2345-91D2-F162C405127D}" name="2" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{877B2BEA-ABD1-4141-9BCB-AE69EC7CD0E1}" name="3" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{E3553FF6-A35E-F24D-8F9B-FDFF853CA939}" name="4" dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{F53C2052-E00C-5D47-94E2-6EEAA85E072A}" name="5" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{35F06D73-5AA1-6B40-9E5F-B9B979ED3AEF}" name="6" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{39F41D5F-D329-AA46-8E9E-8ADB32807EA2}" name="7" dataDxfId="18"/>
+    <tableColumn id="16" xr3:uid="{C1B096E8-3D38-8940-97B2-71D100A0AEFE}" name="8" dataDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{939E4559-1632-1F41-9C13-FEDC9442CD17}" name="9" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{76B6A234-B47B-5648-88B2-B69A0A91AA7F}" name="10" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{4572F0CE-AA1A-FA40-B8BC-8D9A1BE127FD}" name="11a" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{E57F7912-B3EE-6546-A077-CCEDE62E69CB}" name="11b" dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{BE7F2F6D-BF60-B946-A037-26D6B1B11F6E}" name="Q1" dataDxfId="12">
       <calculatedColumnFormula>IF(I2=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{063CA0F4-6645-C64D-83B7-DC255660A115}" name="Q2" dataDxfId="10">
+    <tableColumn id="22" xr3:uid="{063CA0F4-6645-C64D-83B7-DC255660A115}" name="Q2" dataDxfId="11">
       <calculatedColumnFormula>IF(J2=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D9FF7CCF-E3CE-E346-BDFA-80BAB418F49E}" name="Q3" dataDxfId="9">
+    <tableColumn id="23" xr3:uid="{D9FF7CCF-E3CE-E346-BDFA-80BAB418F49E}" name="Q3" dataDxfId="10">
       <calculatedColumnFormula>IF(K2=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{09C89755-22BC-4447-9D0A-0863BC742B45}" name="Q4" dataDxfId="8">
+    <tableColumn id="24" xr3:uid="{09C89755-22BC-4447-9D0A-0863BC742B45}" name="Q4" dataDxfId="9">
       <calculatedColumnFormula>IF(L2=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{BE88876E-C474-3643-A5CC-00B7AD3AA5C8}" name="Q5" dataDxfId="7">
+    <tableColumn id="25" xr3:uid="{BE88876E-C474-3643-A5CC-00B7AD3AA5C8}" name="Q5" dataDxfId="8">
       <calculatedColumnFormula>IF(M2=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{2DCEBFD7-23EB-8042-A4B6-1DE27B9DBEEB}" name="Q6" dataDxfId="6">
+    <tableColumn id="26" xr3:uid="{2DCEBFD7-23EB-8042-A4B6-1DE27B9DBEEB}" name="Q6" dataDxfId="7">
       <calculatedColumnFormula>IF(N2=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6279084C-A701-514B-80D0-60A3AC2988F8}" name="Q7" dataDxfId="5">
+    <tableColumn id="27" xr3:uid="{6279084C-A701-514B-80D0-60A3AC2988F8}" name="Q7" dataDxfId="6">
       <calculatedColumnFormula>IF(O2=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{9F80D501-AEF1-0045-854D-12FF8420DBD3}" name="Q8" dataDxfId="4">
+    <tableColumn id="28" xr3:uid="{9F80D501-AEF1-0045-854D-12FF8420DBD3}" name="Q8" dataDxfId="5">
       <calculatedColumnFormula>IF(P2=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4515,11 +4529,11 @@
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Skill_standard"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Need_OI?"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Content_standard"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="3">
-      <calculatedColumnFormula>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</calculatedColumnFormula>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Pct_Correct" dataDxfId="4">
+      <calculatedColumnFormula>AVERAGE(INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="2">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</calculatedColumnFormula>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Point_Biserial" dataDxfId="3">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$83-_xlpm.item))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Light and Airy" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -4553,7 +4567,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="#"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Framework"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Specifications"/>
-    <tableColumn id="4" xr3:uid="{37E3D24F-9292-BD43-B3FC-16D6A7D0B3AB}" name="Concatenated" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{37E3D24F-9292-BD43-B3FC-16D6A7D0B3AB}" name="Concatenated" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.CONCAT(Table3[[#This Row],['#]],": ",Table3[[#This Row],[Framework]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4784,7 +4798,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AB82"/>
+  <dimension ref="A1:AB83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="10"/>
@@ -4984,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="26">
         <f t="shared" si="0"/>
@@ -5337,7 +5351,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="25" t="b">
         <v>0</v>
@@ -5427,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="32">
         <f t="shared" si="0"/>
@@ -5602,7 +5616,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="31" t="b">
         <v>0</v>
@@ -5691,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="25" t="b">
         <v>0</v>
@@ -5771,7 +5785,7 @@
     </row>
     <row r="12" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10" t="s">
-        <v>785</v>
+        <v>856</v>
       </c>
       <c r="B12" s="28" t="s">
         <v>69</v>
@@ -5780,14 +5794,14 @@
         <v>8</v>
       </c>
       <c r="D12" s="30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="31" t="b">
         <v>0</v>
       </c>
       <c r="F12" s="32">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G12" s="29">
         <f t="shared" si="1"/>
@@ -5795,28 +5809,26 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.25</v>
       </c>
       <c r="I12" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M12" s="29">
         <v>2</v>
       </c>
-      <c r="N12" s="29">
-        <v>3</v>
-      </c>
+      <c r="N12" s="29"/>
       <c r="O12" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P12" s="29">
         <v>3</v>
@@ -5827,19 +5839,19 @@
       <c r="T12" s="29"/>
       <c r="U12" s="32">
         <f>IF(I12=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="29">
         <f>IF(J12=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" s="29">
         <f>IF(K12=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" s="29">
         <f>IF(L12=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="29">
         <f>IF(M12=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -5847,11 +5859,11 @@
       </c>
       <c r="Z12" s="29">
         <f>IF(N12=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="29">
         <f>IF(O12=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" s="29">
         <f>IF(P12=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -5860,23 +5872,23 @@
     </row>
     <row r="13" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13" s="24" t="b">
         <v>0</v>
       </c>
       <c r="E13" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="26">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" s="23">
         <f t="shared" si="1"/>
@@ -5884,7 +5896,7 @@
       </c>
       <c r="H13" s="27">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I13" s="26">
         <v>2</v>
@@ -5905,7 +5917,7 @@
         <v>3</v>
       </c>
       <c r="O13" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P13" s="23">
         <v>3</v>
@@ -5940,7 +5952,7 @@
       </c>
       <c r="AA13" s="23">
         <f>IF(O13=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="23">
         <f>IF(P13=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -5949,7 +5961,7 @@
     </row>
     <row r="14" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B14" s="28" t="s">
         <v>69</v>
@@ -6038,7 +6050,7 @@
     </row>
     <row r="15" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>69</v>
@@ -6054,7 +6066,7 @@
       </c>
       <c r="F15" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G15" s="23">
         <f t="shared" si="1"/>
@@ -6062,16 +6074,16 @@
       </c>
       <c r="H15" s="27">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I15" s="26">
         <v>2</v>
       </c>
       <c r="J15" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L15" s="23">
         <v>3</v>
@@ -6080,7 +6092,7 @@
         <v>2</v>
       </c>
       <c r="N15" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O15" s="23">
         <v>3</v>
@@ -6098,11 +6110,11 @@
       </c>
       <c r="V15" s="23">
         <f>IF(J15=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="23">
         <f>IF(K15=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="23">
         <f>IF(L15=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6114,7 +6126,7 @@
       </c>
       <c r="Z15" s="23">
         <f>IF(N15=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15" s="23">
         <f>IF(O15=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6127,7 +6139,7 @@
     </row>
     <row r="16" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B16" s="28" t="s">
         <v>69</v>
@@ -6139,11 +6151,11 @@
         <v>0</v>
       </c>
       <c r="E16" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="32">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" s="29">
         <f t="shared" si="1"/>
@@ -6151,16 +6163,16 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I16" s="32">
         <v>2</v>
       </c>
       <c r="J16" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L16" s="29">
         <v>3</v>
@@ -6169,7 +6181,7 @@
         <v>2</v>
       </c>
       <c r="N16" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O16" s="29">
         <v>3</v>
@@ -6191,7 +6203,7 @@
       </c>
       <c r="W16" s="29">
         <f>IF(K16=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" s="29">
         <f>IF(L16=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6203,7 +6215,7 @@
       </c>
       <c r="Z16" s="29">
         <f>IF(N16=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="29">
         <f>IF(O16=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6216,7 +6228,7 @@
     </row>
     <row r="17" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>69</v>
@@ -6232,7 +6244,7 @@
       </c>
       <c r="F17" s="26">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G17" s="23">
         <f t="shared" si="1"/>
@@ -6240,28 +6252,28 @@
       </c>
       <c r="H17" s="27">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I17" s="26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="23">
         <v>1</v>
       </c>
       <c r="L17" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P17" s="23">
         <v>3</v>
@@ -6272,11 +6284,11 @@
       <c r="T17" s="23"/>
       <c r="U17" s="26">
         <f>IF(I17=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="23">
         <f>IF(J17=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" s="23">
         <f>IF(K17=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6284,19 +6296,19 @@
       </c>
       <c r="X17" s="23">
         <f>IF(L17=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="23">
         <f>IF(M17=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" s="23">
         <f>IF(N17=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" s="23">
         <f>IF(O17=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" s="23">
         <f>IF(P17=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6305,23 +6317,23 @@
     </row>
     <row r="18" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>69</v>
       </c>
       <c r="C18" s="29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18" s="30" t="b">
         <v>0</v>
       </c>
       <c r="E18" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="32">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G18" s="29">
         <f t="shared" si="1"/>
@@ -6329,28 +6341,28 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I18" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="29">
         <v>2</v>
       </c>
       <c r="K18" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O18" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P18" s="29">
         <v>3</v>
@@ -6361,7 +6373,7 @@
       <c r="T18" s="29"/>
       <c r="U18" s="32">
         <f>IF(I18=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="29">
         <f>IF(J18=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6369,7 +6381,7 @@
       </c>
       <c r="W18" s="29">
         <f>IF(K18=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" s="29">
         <f>IF(L18=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6377,15 +6389,15 @@
       </c>
       <c r="Y18" s="29">
         <f>IF(M18=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="29">
         <f>IF(N18=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="29">
         <f>IF(O18=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="29">
         <f>IF(P18=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6394,7 +6406,7 @@
     </row>
     <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>69</v>
@@ -6410,7 +6422,7 @@
       </c>
       <c r="F19" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" s="23">
         <f t="shared" si="1"/>
@@ -6418,22 +6430,22 @@
       </c>
       <c r="H19" s="27">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="I19" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="23">
         <v>2</v>
       </c>
       <c r="K19" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M19" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="23">
         <v>3</v>
@@ -6442,7 +6454,7 @@
         <v>3</v>
       </c>
       <c r="P19" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="26"/>
       <c r="R19" s="23"/>
@@ -6450,7 +6462,7 @@
       <c r="T19" s="23"/>
       <c r="U19" s="26">
         <f>IF(I19=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="23">
         <f>IF(J19=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6458,15 +6470,15 @@
       </c>
       <c r="W19" s="23">
         <f>IF(K19=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" s="23">
         <f>IF(L19=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="23">
         <f>IF(M19=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="23">
         <f>IF(N19=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6478,12 +6490,12 @@
       </c>
       <c r="AB19" s="23">
         <f>IF(P19=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B20" s="28" t="s">
         <v>69</v>
@@ -6495,11 +6507,11 @@
         <v>0</v>
       </c>
       <c r="E20" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="32">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="29">
         <f t="shared" si="1"/>
@@ -6507,10 +6519,10 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I20" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="29">
         <v>2</v>
@@ -6522,16 +6534,16 @@
         <v>3</v>
       </c>
       <c r="M20" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" s="29">
         <v>3</v>
       </c>
       <c r="O20" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P20" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="32"/>
       <c r="R20" s="29"/>
@@ -6539,7 +6551,7 @@
       <c r="T20" s="29"/>
       <c r="U20" s="32">
         <f>IF(I20=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="29">
         <f>IF(J20=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6555,7 +6567,7 @@
       </c>
       <c r="Y20" s="29">
         <f>IF(M20=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="29">
         <f>IF(N20=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6563,16 +6575,16 @@
       </c>
       <c r="AA20" s="29">
         <f>IF(O20=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" s="29">
         <f>IF(P20=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="10" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>69</v>
@@ -6584,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="26">
         <f t="shared" si="0"/>
@@ -6617,10 +6629,10 @@
         <v>3</v>
       </c>
       <c r="O21" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P21" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="26"/>
       <c r="R21" s="23"/>
@@ -6652,22 +6664,22 @@
       </c>
       <c r="AA21" s="23">
         <f>IF(O21=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="23">
         <f>IF(P21=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B22" s="28" t="s">
         <v>69</v>
       </c>
       <c r="C22" s="29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22" s="30" t="b">
         <v>0</v>
@@ -6694,7 +6706,7 @@
         <v>2</v>
       </c>
       <c r="K22" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L22" s="29">
         <v>3</v>
@@ -6709,7 +6721,7 @@
         <v>3</v>
       </c>
       <c r="P22" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="32"/>
       <c r="R22" s="29"/>
@@ -6725,7 +6737,7 @@
       </c>
       <c r="W22" s="29">
         <f>IF(K22=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="29">
         <f>IF(L22=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6745,12 +6757,12 @@
       </c>
       <c r="AB22" s="29">
         <f>IF(P22=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B23" s="22" t="s">
         <v>69</v>
@@ -6839,7 +6851,7 @@
     </row>
     <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="10" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B24" s="28" t="s">
         <v>69</v>
@@ -6855,7 +6867,7 @@
       </c>
       <c r="F24" s="32">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G24" s="29">
         <f t="shared" si="1"/>
@@ -6863,7 +6875,7 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I24" s="32">
         <v>2</v>
@@ -6872,7 +6884,7 @@
         <v>2</v>
       </c>
       <c r="K24" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" s="29">
         <v>3</v>
@@ -6903,7 +6915,7 @@
       </c>
       <c r="W24" s="29">
         <f>IF(K24=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" s="29">
         <f>IF(L24=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6928,7 +6940,7 @@
     </row>
     <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>69</v>
@@ -6940,11 +6952,11 @@
         <v>0</v>
       </c>
       <c r="E25" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G25" s="23">
         <f t="shared" si="1"/>
@@ -6952,25 +6964,25 @@
       </c>
       <c r="H25" s="27">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I25" s="26">
         <v>2</v>
       </c>
       <c r="J25" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="23">
         <v>1</v>
       </c>
       <c r="L25" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M25" s="23">
         <v>2</v>
       </c>
       <c r="N25" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O25" s="23">
         <v>3</v>
@@ -6988,7 +7000,7 @@
       </c>
       <c r="V25" s="23">
         <f>IF(J25=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="23">
         <f>IF(K25=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -6996,7 +7008,7 @@
       </c>
       <c r="X25" s="23">
         <f>IF(L25=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" s="23">
         <f>IF(M25=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7004,7 +7016,7 @@
       </c>
       <c r="Z25" s="23">
         <f>IF(N25=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25" s="23">
         <f>IF(O25=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7017,23 +7029,23 @@
     </row>
     <row r="26" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B26" s="28" t="s">
         <v>69</v>
       </c>
       <c r="C26" s="29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" s="30" t="b">
         <v>0</v>
       </c>
       <c r="E26" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="32">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" s="29">
         <f t="shared" si="1"/>
@@ -7041,13 +7053,13 @@
       </c>
       <c r="H26" s="33">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I26" s="32">
         <v>2</v>
       </c>
       <c r="J26" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="29">
         <v>1</v>
@@ -7059,7 +7071,7 @@
         <v>2</v>
       </c>
       <c r="N26" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O26" s="29">
         <v>3</v>
@@ -7077,7 +7089,7 @@
       </c>
       <c r="V26" s="29">
         <f>IF(J26=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" s="29">
         <f>IF(K26=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7106,7 +7118,7 @@
     </row>
     <row r="27" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>69</v>
@@ -7122,7 +7134,7 @@
       </c>
       <c r="F27" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="23">
         <f t="shared" si="1"/>
@@ -7130,7 +7142,7 @@
       </c>
       <c r="H27" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="I27" s="26">
         <v>2</v>
@@ -7139,16 +7151,16 @@
         <v>2</v>
       </c>
       <c r="K27" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M27" s="23">
         <v>2</v>
       </c>
       <c r="N27" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O27" s="23">
         <v>3</v>
@@ -7170,11 +7182,11 @@
       </c>
       <c r="W27" s="23">
         <f>IF(K27=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" s="23">
         <f>IF(L27=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="23">
         <f>IF(M27=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7182,7 +7194,7 @@
       </c>
       <c r="Z27" s="23">
         <f>IF(N27=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="23">
         <f>IF(O27=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7195,7 +7207,7 @@
     </row>
     <row r="28" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B28" s="28" t="s">
         <v>69</v>
@@ -7207,11 +7219,11 @@
         <v>0</v>
       </c>
       <c r="E28" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="32">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="29">
         <f t="shared" si="1"/>
@@ -7219,7 +7231,7 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I28" s="32">
         <v>2</v>
@@ -7228,7 +7240,7 @@
         <v>2</v>
       </c>
       <c r="K28" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" s="29">
         <v>3</v>
@@ -7259,7 +7271,7 @@
       </c>
       <c r="W28" s="29">
         <f>IF(K28=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" s="29">
         <f>IF(L28=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7284,7 +7296,7 @@
     </row>
     <row r="29" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>69</v>
@@ -7300,7 +7312,7 @@
       </c>
       <c r="F29" s="26">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G29" s="23">
         <f t="shared" si="1"/>
@@ -7308,7 +7320,7 @@
       </c>
       <c r="H29" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I29" s="26">
         <v>2</v>
@@ -7317,7 +7329,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L29" s="23">
         <v>3</v>
@@ -7332,7 +7344,7 @@
         <v>3</v>
       </c>
       <c r="P29" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q29" s="26"/>
       <c r="R29" s="23"/>
@@ -7348,7 +7360,7 @@
       </c>
       <c r="W29" s="23">
         <f>IF(K29=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" s="23">
         <f>IF(L29=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7368,12 +7380,12 @@
       </c>
       <c r="AB29" s="23">
         <f>IF(P29=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B30" s="28" t="s">
         <v>69</v>
@@ -7389,7 +7401,7 @@
       </c>
       <c r="F30" s="32">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" s="29">
         <f t="shared" si="1"/>
@@ -7397,31 +7409,31 @@
       </c>
       <c r="H30" s="33">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="I30" s="32">
+        <v>2</v>
+      </c>
+      <c r="J30" s="29">
+        <v>2</v>
+      </c>
+      <c r="K30" s="29">
+        <v>3</v>
+      </c>
+      <c r="L30" s="29">
+        <v>3</v>
+      </c>
+      <c r="M30" s="29">
+        <v>2</v>
+      </c>
+      <c r="N30" s="29">
+        <v>3</v>
+      </c>
+      <c r="O30" s="29">
+        <v>3</v>
+      </c>
+      <c r="P30" s="29">
         <v>4</v>
-      </c>
-      <c r="J30" s="29">
-        <v>2</v>
-      </c>
-      <c r="K30" s="29">
-        <v>2</v>
-      </c>
-      <c r="L30" s="29">
-        <v>1</v>
-      </c>
-      <c r="M30" s="29">
-        <v>2</v>
-      </c>
-      <c r="N30" s="29">
-        <v>3</v>
-      </c>
-      <c r="O30" s="29">
-        <v>3</v>
-      </c>
-      <c r="P30" s="29">
-        <v>3</v>
       </c>
       <c r="Q30" s="32"/>
       <c r="R30" s="29"/>
@@ -7429,7 +7441,7 @@
       <c r="T30" s="29"/>
       <c r="U30" s="32">
         <f>IF(I30=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="29">
         <f>IF(J30=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7441,7 +7453,7 @@
       </c>
       <c r="X30" s="29">
         <f>IF(L30=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" s="29">
         <f>IF(M30=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7457,12 +7469,12 @@
       </c>
       <c r="AB30" s="29">
         <f>IF(P30=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>69</v>
@@ -7478,7 +7490,7 @@
       </c>
       <c r="F31" s="26">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" s="23">
         <f t="shared" si="1"/>
@@ -7486,19 +7498,19 @@
       </c>
       <c r="H31" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I31" s="26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K31" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M31" s="23">
         <v>2</v>
@@ -7518,11 +7530,11 @@
       <c r="T31" s="23"/>
       <c r="U31" s="26">
         <f>IF(I31=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="23">
         <f>IF(J31=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="23">
         <f>IF(K31=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7530,7 +7542,7 @@
       </c>
       <c r="X31" s="23">
         <f>IF(L31=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="23">
         <f>IF(M31=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7551,7 +7563,7 @@
     </row>
     <row r="32" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B32" s="28" t="s">
         <v>69</v>
@@ -7567,7 +7579,7 @@
       </c>
       <c r="F32" s="32">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G32" s="29">
         <f t="shared" si="1"/>
@@ -7575,16 +7587,16 @@
       </c>
       <c r="H32" s="33">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="I32" s="32">
         <v>2</v>
       </c>
       <c r="J32" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K32" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L32" s="29">
         <v>3</v>
@@ -7611,11 +7623,11 @@
       </c>
       <c r="V32" s="29">
         <f>IF(J32=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32" s="29">
         <f>IF(K32=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X32" s="29">
         <f>IF(L32=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7640,7 +7652,7 @@
     </row>
     <row r="33" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B33" s="22" t="s">
         <v>69</v>
@@ -7656,7 +7668,7 @@
       </c>
       <c r="F33" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33" s="23">
         <f t="shared" si="1"/>
@@ -7664,7 +7676,7 @@
       </c>
       <c r="H33" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I33" s="26">
         <v>2</v>
@@ -7685,7 +7697,7 @@
         <v>3</v>
       </c>
       <c r="O33" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P33" s="23">
         <v>3</v>
@@ -7720,7 +7732,7 @@
       </c>
       <c r="AA33" s="23">
         <f>IF(O33=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" s="23">
         <f>IF(P33=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7729,7 +7741,7 @@
     </row>
     <row r="34" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B34" s="28" t="s">
         <v>69</v>
@@ -7818,7 +7830,7 @@
     </row>
     <row r="35" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B35" s="22" t="s">
         <v>69</v>
@@ -7834,7 +7846,7 @@
       </c>
       <c r="F35" s="26">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G35" s="23">
         <f t="shared" si="1"/>
@@ -7842,7 +7854,7 @@
       </c>
       <c r="H35" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I35" s="26">
         <v>2</v>
@@ -7851,7 +7863,7 @@
         <v>2</v>
       </c>
       <c r="K35" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L35" s="23">
         <v>3</v>
@@ -7882,7 +7894,7 @@
       </c>
       <c r="W35" s="23">
         <f>IF(K35=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" s="23">
         <f>IF(L35=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7907,7 +7919,7 @@
     </row>
     <row r="36" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B36" s="28" t="s">
         <v>69</v>
@@ -7923,7 +7935,7 @@
       </c>
       <c r="F36" s="32">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G36" s="29">
         <f t="shared" si="1"/>
@@ -7931,10 +7943,10 @@
       </c>
       <c r="H36" s="33">
         <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.5</v>
       </c>
       <c r="I36" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="29">
         <v>2</v>
@@ -7943,19 +7955,19 @@
         <v>4</v>
       </c>
       <c r="L36" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M36" s="29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N36" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O36" s="29">
         <v>1</v>
       </c>
       <c r="P36" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q36" s="32"/>
       <c r="R36" s="29"/>
@@ -7963,7 +7975,7 @@
       <c r="T36" s="29"/>
       <c r="U36" s="32">
         <f>IF(I36=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="29">
         <f>IF(J36=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7975,15 +7987,15 @@
       </c>
       <c r="X36" s="29">
         <f>IF(L36=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" s="29">
         <f>IF(M36=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z36" s="29">
         <f>IF(N36=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA36" s="29">
         <f>IF(O36=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -7991,12 +8003,12 @@
       </c>
       <c r="AB36" s="29">
         <f>IF(P36=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B37" s="22" t="s">
         <v>69</v>
@@ -8012,7 +8024,7 @@
       </c>
       <c r="F37" s="26">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G37" s="23">
         <f t="shared" si="1"/>
@@ -8020,31 +8032,31 @@
       </c>
       <c r="H37" s="27">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="I37" s="26">
         <v>1</v>
       </c>
       <c r="J37" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="23">
         <v>4</v>
       </c>
       <c r="L37" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M37" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N37" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O37" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P37" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="26"/>
       <c r="R37" s="23"/>
@@ -8056,7 +8068,7 @@
       </c>
       <c r="V37" s="23">
         <f>IF(J37=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="23">
         <f>IF(K37=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8064,19 +8076,19 @@
       </c>
       <c r="X37" s="23">
         <f>IF(L37=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" s="23">
         <f>IF(M37=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="23">
         <f>IF(N37=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="23">
         <f>IF(O37=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="23">
         <f>IF(P37=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8085,7 +8097,7 @@
     </row>
     <row r="38" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B38" s="28" t="s">
         <v>69</v>
@@ -8101,7 +8113,7 @@
       </c>
       <c r="F38" s="32">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G38" s="29">
         <f t="shared" si="1"/>
@@ -8109,16 +8121,16 @@
       </c>
       <c r="H38" s="33">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I38" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" s="29">
         <v>1</v>
       </c>
       <c r="K38" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L38" s="29">
         <v>3</v>
@@ -8141,7 +8153,7 @@
       <c r="T38" s="29"/>
       <c r="U38" s="32">
         <f>IF(I38=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="29">
         <f>IF(J38=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8149,7 +8161,7 @@
       </c>
       <c r="W38" s="29">
         <f>IF(K38=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" s="29">
         <f>IF(L38=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8174,7 +8186,7 @@
     </row>
     <row r="39" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B39" s="22" t="s">
         <v>69</v>
@@ -8190,7 +8202,7 @@
       </c>
       <c r="F39" s="26">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G39" s="23">
         <f t="shared" si="1"/>
@@ -8198,13 +8210,13 @@
       </c>
       <c r="H39" s="27">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="I39" s="26">
         <v>2</v>
       </c>
       <c r="J39" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K39" s="23">
         <v>1</v>
@@ -8222,7 +8234,7 @@
         <v>3</v>
       </c>
       <c r="P39" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="26"/>
       <c r="R39" s="23"/>
@@ -8234,7 +8246,7 @@
       </c>
       <c r="V39" s="23">
         <f>IF(J39=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W39" s="23">
         <f>IF(K39=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8258,28 +8270,28 @@
       </c>
       <c r="AB39" s="23">
         <f>IF(P39=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C40" s="29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D40" s="30" t="b">
         <v>0</v>
       </c>
       <c r="E40" s="31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="32">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G40" s="29">
         <f t="shared" si="1"/>
@@ -8287,28 +8299,28 @@
       </c>
       <c r="H40" s="33">
         <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I40" s="32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J40" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L40" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M40" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O40" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P40" s="29">
         <v>3</v>
@@ -8319,31 +8331,31 @@
       <c r="T40" s="29"/>
       <c r="U40" s="32">
         <f>IF(I40=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="29">
         <f>IF(J40=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="29">
         <f>IF(K40=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" s="29">
         <f>IF(L40=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="29">
         <f>IF(M40=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z40" s="29">
         <f>IF(N40=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA40" s="29">
         <f>IF(O40=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" s="29">
         <f>IF(P40=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8352,7 +8364,7 @@
     </row>
     <row r="41" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B41" s="22" t="s">
         <v>46</v>
@@ -8364,11 +8376,11 @@
         <v>0</v>
       </c>
       <c r="E41" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G41" s="23">
         <f t="shared" si="1"/>
@@ -8376,28 +8388,28 @@
       </c>
       <c r="H41" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="I41" s="26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J41" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L41" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M41" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N41" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O41" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P41" s="23">
         <v>3</v>
@@ -8408,23 +8420,23 @@
       <c r="T41" s="23"/>
       <c r="U41" s="26">
         <f>IF(I41=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="23">
         <f>IF(J41=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" s="23">
         <f>IF(K41=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X41" s="23">
         <f>IF(L41=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="23">
         <f>IF(M41=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z41" s="23">
         <f>IF(N41=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8432,7 +8444,7 @@
       </c>
       <c r="AA41" s="23">
         <f>IF(O41=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="23">
         <f>IF(P41=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8441,7 +8453,7 @@
     </row>
     <row r="42" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B42" s="28" t="s">
         <v>46</v>
@@ -8468,7 +8480,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="I42" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="29">
         <v>2</v>
@@ -8483,7 +8495,7 @@
         <v>2</v>
       </c>
       <c r="N42" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O42" s="29">
         <v>3</v>
@@ -8497,7 +8509,7 @@
       <c r="T42" s="29"/>
       <c r="U42" s="32">
         <f>IF(I42=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="29">
         <f>IF(J42=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8517,7 +8529,7 @@
       </c>
       <c r="Z42" s="29">
         <f>IF(N42=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="29">
         <f>IF(O42=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8530,7 +8542,7 @@
     </row>
     <row r="43" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B43" s="22" t="s">
         <v>46</v>
@@ -8542,11 +8554,11 @@
         <v>0</v>
       </c>
       <c r="E43" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="26">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G43" s="23">
         <f t="shared" si="1"/>
@@ -8554,31 +8566,31 @@
       </c>
       <c r="H43" s="27">
         <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I43" s="26">
         <v>1</v>
       </c>
       <c r="J43" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L43" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M43" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N43" s="23">
         <v>3</v>
       </c>
       <c r="O43" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P43" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="26"/>
       <c r="R43" s="23"/>
@@ -8590,19 +8602,19 @@
       </c>
       <c r="V43" s="23">
         <f>IF(J43=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="23">
         <f>IF(K43=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" s="23">
         <f>IF(L43=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" s="23">
         <f>IF(M43=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z43" s="23">
         <f>IF(N43=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8610,16 +8622,16 @@
       </c>
       <c r="AA43" s="23">
         <f>IF(O43=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB43" s="23">
         <f>IF(P43=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B44" s="28" t="s">
         <v>46</v>
@@ -8631,11 +8643,11 @@
         <v>0</v>
       </c>
       <c r="E44" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="32">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G44" s="29">
         <f t="shared" si="1"/>
@@ -8643,31 +8655,31 @@
       </c>
       <c r="H44" s="33">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="I44" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K44" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L44" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M44" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N44" s="29">
         <v>3</v>
       </c>
       <c r="O44" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P44" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="32"/>
       <c r="R44" s="29"/>
@@ -8675,11 +8687,11 @@
       <c r="T44" s="29"/>
       <c r="U44" s="32">
         <f>IF(I44=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="29">
         <f>IF(J44=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" s="29">
         <f>IF(K44=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8687,11 +8699,11 @@
       </c>
       <c r="X44" s="29">
         <f>IF(L44=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="29">
         <f>IF(M44=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="29">
         <f>IF(N44=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8699,16 +8711,16 @@
       </c>
       <c r="AA44" s="29">
         <f>IF(O44=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" s="29">
         <f>IF(P44=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B45" s="22" t="s">
         <v>46</v>
@@ -8720,11 +8732,11 @@
         <v>0</v>
       </c>
       <c r="E45" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="26">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G45" s="23">
         <f t="shared" si="1"/>
@@ -8732,31 +8744,31 @@
       </c>
       <c r="H45" s="27">
         <f t="shared" si="2"/>
-        <v>0.16666666666666666</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I45" s="26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J45" s="23">
         <v>2</v>
       </c>
       <c r="K45" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="23">
         <v>3</v>
       </c>
       <c r="M45" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O45" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P45" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="26"/>
       <c r="R45" s="23"/>
@@ -8764,7 +8776,7 @@
       <c r="T45" s="23"/>
       <c r="U45" s="26">
         <f>IF(I45=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="23">
         <f>IF(J45=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8780,24 +8792,24 @@
       </c>
       <c r="Y45" s="23">
         <f>IF(M45=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z45" s="23">
         <f>IF(N45=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA45" s="23">
         <f>IF(O45=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" s="23">
         <f>IF(P45=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B46" s="28" t="s">
         <v>46</v>
@@ -8809,11 +8821,11 @@
         <v>0</v>
       </c>
       <c r="E46" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="32">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="29">
         <f t="shared" si="1"/>
@@ -8821,28 +8833,32 @@
       </c>
       <c r="H46" s="33">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="I46" s="32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46" s="29">
         <v>2</v>
       </c>
       <c r="K46" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M46" s="29">
         <v>1</v>
       </c>
       <c r="N46" s="29">
-        <v>3</v>
-      </c>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
+        <v>2</v>
+      </c>
+      <c r="O46" s="29">
+        <v>1</v>
+      </c>
+      <c r="P46" s="29">
+        <v>2</v>
+      </c>
       <c r="Q46" s="32"/>
       <c r="R46" s="29"/>
       <c r="S46" s="29"/>
@@ -8857,11 +8873,11 @@
       </c>
       <c r="W46" s="29">
         <f>IF(K46=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" s="29">
         <f>IF(L46=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" s="29">
         <f>IF(M46=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8869,7 +8885,7 @@
       </c>
       <c r="Z46" s="29">
         <f>IF(N46=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="29">
         <f>IF(O46=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8882,7 +8898,7 @@
     </row>
     <row r="47" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B47" s="22" t="s">
         <v>46</v>
@@ -8898,7 +8914,7 @@
       </c>
       <c r="F47" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G47" s="23">
         <f t="shared" si="1"/>
@@ -8906,7 +8922,7 @@
       </c>
       <c r="H47" s="27">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.25</v>
       </c>
       <c r="I47" s="26">
         <v>1</v>
@@ -8918,20 +8934,16 @@
         <v>1</v>
       </c>
       <c r="L47" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M47" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N47" s="23">
         <v>3</v>
       </c>
-      <c r="O47" s="23">
-        <v>1</v>
-      </c>
-      <c r="P47" s="23">
-        <v>2</v>
-      </c>
+      <c r="O47" s="23"/>
+      <c r="P47" s="23"/>
       <c r="Q47" s="26"/>
       <c r="R47" s="23"/>
       <c r="S47" s="23"/>
@@ -8950,11 +8962,11 @@
       </c>
       <c r="X47" s="23">
         <f>IF(L47=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" s="23">
         <f>IF(M47=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="23">
         <f>IF(N47=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -8971,7 +8983,7 @@
     </row>
     <row r="48" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>46</v>
@@ -8983,11 +8995,11 @@
         <v>0</v>
       </c>
       <c r="E48" s="31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G48" s="29">
         <f t="shared" si="1"/>
@@ -8995,10 +9007,10 @@
       </c>
       <c r="H48" s="33">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I48" s="32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48" s="29">
         <v>2</v>
@@ -9007,19 +9019,19 @@
         <v>1</v>
       </c>
       <c r="L48" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M48" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N48" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O48" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P48" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="32"/>
       <c r="R48" s="29"/>
@@ -9039,15 +9051,15 @@
       </c>
       <c r="X48" s="29">
         <f>IF(L48=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" s="29">
         <f>IF(M48=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="29">
         <f>IF(N48=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA48" s="29">
         <f>IF(O48=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9055,12 +9067,12 @@
       </c>
       <c r="AB48" s="29">
         <f>IF(P48=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B49" s="22" t="s">
         <v>46</v>
@@ -9072,11 +9084,11 @@
         <v>0</v>
       </c>
       <c r="E49" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G49" s="23">
         <f t="shared" si="1"/>
@@ -9084,10 +9096,10 @@
       </c>
       <c r="H49" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.25</v>
       </c>
       <c r="I49" s="26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" s="23">
         <v>2</v>
@@ -9096,16 +9108,16 @@
         <v>1</v>
       </c>
       <c r="L49" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M49" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N49" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O49" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P49" s="23">
         <v>3</v>
@@ -9128,19 +9140,19 @@
       </c>
       <c r="X49" s="23">
         <f>IF(L49=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="23">
         <f>IF(M49=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="23">
         <f>IF(N49=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="23">
         <f>IF(O49=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" s="23">
         <f>IF(P49=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9149,7 +9161,7 @@
     </row>
     <row r="50" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B50" s="28" t="s">
         <v>46</v>
@@ -9176,7 +9188,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="I50" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" s="29">
         <v>2</v>
@@ -9194,7 +9206,7 @@
         <v>3</v>
       </c>
       <c r="O50" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P50" s="29">
         <v>3</v>
@@ -9205,7 +9217,7 @@
       <c r="T50" s="29"/>
       <c r="U50" s="32">
         <f>IF(I50=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" s="29">
         <f>IF(J50=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9229,7 +9241,7 @@
       </c>
       <c r="AA50" s="29">
         <f>IF(O50=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50" s="29">
         <f>IF(P50=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9238,7 +9250,7 @@
     </row>
     <row r="51" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B51" s="22" t="s">
         <v>46</v>
@@ -9254,7 +9266,7 @@
       </c>
       <c r="F51" s="26">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G51" s="23">
         <f t="shared" si="1"/>
@@ -9262,28 +9274,28 @@
       </c>
       <c r="H51" s="27">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I51" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" s="23">
         <v>2</v>
       </c>
       <c r="K51" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L51" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M51" s="23">
         <v>2</v>
       </c>
       <c r="N51" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O51" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P51" s="23">
         <v>3</v>
@@ -9294,7 +9306,7 @@
       <c r="T51" s="23"/>
       <c r="U51" s="26">
         <f>IF(I51=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="23">
         <f>IF(J51=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9302,11 +9314,11 @@
       </c>
       <c r="W51" s="23">
         <f>IF(K51=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51" s="23">
         <f>IF(L51=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51" s="23">
         <f>IF(M51=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9314,11 +9326,11 @@
       </c>
       <c r="Z51" s="23">
         <f>IF(N51=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA51" s="23">
         <f>IF(O51=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB51" s="23">
         <f>IF(P51=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9327,7 +9339,7 @@
     </row>
     <row r="52" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B52" s="28" t="s">
         <v>46</v>
@@ -9339,11 +9351,11 @@
         <v>0</v>
       </c>
       <c r="E52" s="31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="32">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G52" s="29">
         <f t="shared" si="1"/>
@@ -9351,28 +9363,28 @@
       </c>
       <c r="H52" s="33">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I52" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" s="29">
         <v>2</v>
       </c>
       <c r="K52" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M52" s="29">
         <v>2</v>
       </c>
       <c r="N52" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O52" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P52" s="29">
         <v>3</v>
@@ -9383,7 +9395,7 @@
       <c r="T52" s="29"/>
       <c r="U52" s="32">
         <f>IF(I52=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" s="29">
         <f>IF(J52=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9391,11 +9403,11 @@
       </c>
       <c r="W52" s="29">
         <f>IF(K52=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X52" s="29">
         <f>IF(L52=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="29">
         <f>IF(M52=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9403,11 +9415,11 @@
       </c>
       <c r="Z52" s="29">
         <f>IF(N52=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="29">
         <f>IF(O52=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB52" s="29">
         <f>IF(P52=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9416,7 +9428,7 @@
     </row>
     <row r="53" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B53" s="22" t="s">
         <v>46</v>
@@ -9428,11 +9440,11 @@
         <v>0</v>
       </c>
       <c r="E53" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G53" s="23">
         <f t="shared" si="1"/>
@@ -9440,7 +9452,7 @@
       </c>
       <c r="H53" s="27">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I53" s="26">
         <v>2</v>
@@ -9449,7 +9461,7 @@
         <v>2</v>
       </c>
       <c r="K53" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="23">
         <v>3</v>
@@ -9461,10 +9473,10 @@
         <v>3</v>
       </c>
       <c r="O53" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P53" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="26"/>
       <c r="R53" s="23"/>
@@ -9480,7 +9492,7 @@
       </c>
       <c r="W53" s="23">
         <f>IF(K53=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="23">
         <f>IF(L53=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9500,12 +9512,12 @@
       </c>
       <c r="AB53" s="23">
         <f>IF(P53=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B54" s="28" t="s">
         <v>46</v>
@@ -9517,11 +9529,11 @@
         <v>0</v>
       </c>
       <c r="E54" s="31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="32">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G54" s="29">
         <f t="shared" si="1"/>
@@ -9529,16 +9541,16 @@
       </c>
       <c r="H54" s="33">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I54" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" s="29">
         <v>2</v>
       </c>
       <c r="K54" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="29">
         <v>3</v>
@@ -9547,13 +9559,13 @@
         <v>2</v>
       </c>
       <c r="N54" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O54" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P54" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q54" s="32"/>
       <c r="R54" s="29"/>
@@ -9561,7 +9573,7 @@
       <c r="T54" s="29"/>
       <c r="U54" s="32">
         <f>IF(I54=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" s="29">
         <f>IF(J54=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9569,7 +9581,7 @@
       </c>
       <c r="W54" s="29">
         <f>IF(K54=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54" s="29">
         <f>IF(L54=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9581,20 +9593,20 @@
       </c>
       <c r="Z54" s="29">
         <f>IF(N54=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA54" s="29">
         <f>IF(O54=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB54" s="29">
         <f>IF(P54=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B55" s="22" t="s">
         <v>46</v>
@@ -9606,11 +9618,11 @@
         <v>0</v>
       </c>
       <c r="E55" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="26">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G55" s="23">
         <f t="shared" si="1"/>
@@ -9618,31 +9630,31 @@
       </c>
       <c r="H55" s="27">
         <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.5</v>
       </c>
       <c r="I55" s="26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J55" s="23">
+        <v>2</v>
+      </c>
+      <c r="K55" s="23">
+        <v>1</v>
+      </c>
+      <c r="L55" s="23">
+        <v>3</v>
+      </c>
+      <c r="M55" s="23">
+        <v>2</v>
+      </c>
+      <c r="N55" s="23">
         <v>4</v>
       </c>
-      <c r="K55" s="23">
-        <v>4</v>
-      </c>
-      <c r="L55" s="23">
-        <v>3</v>
-      </c>
-      <c r="M55" s="23">
-        <v>3</v>
-      </c>
-      <c r="N55" s="23">
-        <v>1</v>
-      </c>
       <c r="O55" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P55" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q55" s="26"/>
       <c r="R55" s="23"/>
@@ -9654,11 +9666,11 @@
       </c>
       <c r="V55" s="23">
         <f>IF(J55=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="23">
         <f>IF(K55=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55" s="23">
         <f>IF(L55=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9666,7 +9678,7 @@
       </c>
       <c r="Y55" s="23">
         <f>IF(M55=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z55" s="23">
         <f>IF(N55=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9674,16 +9686,16 @@
       </c>
       <c r="AA55" s="23">
         <f>IF(O55=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB55" s="23">
         <f>IF(P55=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B56" s="28" t="s">
         <v>46</v>
@@ -9695,11 +9707,11 @@
         <v>0</v>
       </c>
       <c r="E56" s="31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="32">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G56" s="29">
         <f t="shared" si="1"/>
@@ -9707,7 +9719,7 @@
       </c>
       <c r="H56" s="33">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="I56" s="32">
         <v>3</v>
@@ -9716,22 +9728,22 @@
         <v>4</v>
       </c>
       <c r="K56" s="29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L56" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56" s="29">
+        <v>3</v>
+      </c>
+      <c r="N56" s="29">
+        <v>1</v>
+      </c>
+      <c r="O56" s="29">
+        <v>2</v>
+      </c>
+      <c r="P56" s="29">
         <v>4</v>
-      </c>
-      <c r="N56" s="29">
-        <v>3</v>
-      </c>
-      <c r="O56" s="29">
-        <v>3</v>
-      </c>
-      <c r="P56" s="29">
-        <v>1</v>
       </c>
       <c r="Q56" s="32"/>
       <c r="R56" s="29"/>
@@ -9747,11 +9759,11 @@
       </c>
       <c r="W56" s="29">
         <f>IF(K56=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X56" s="29">
         <f>IF(L56=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" s="29">
         <f>IF(M56=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9759,11 +9771,11 @@
       </c>
       <c r="Z56" s="29">
         <f>IF(N56=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA56" s="29">
         <f>IF(O56=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB56" s="29">
         <f>IF(P56=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9772,23 +9784,23 @@
     </row>
     <row r="57" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B57" s="22" t="s">
         <v>46</v>
       </c>
       <c r="C57" s="23">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D57" s="24" t="b">
         <v>0</v>
       </c>
       <c r="E57" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="26">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G57" s="23">
         <f t="shared" si="1"/>
@@ -9796,57 +9808,63 @@
       </c>
       <c r="H57" s="27">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="I57" s="26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K57" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L57" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M57" s="23">
-        <v>2</v>
-      </c>
-      <c r="N57" s="23"/>
-      <c r="O57" s="23"/>
-      <c r="P57" s="23"/>
+        <v>4</v>
+      </c>
+      <c r="N57" s="23">
+        <v>3</v>
+      </c>
+      <c r="O57" s="23">
+        <v>3</v>
+      </c>
+      <c r="P57" s="23">
+        <v>1</v>
+      </c>
       <c r="Q57" s="26"/>
       <c r="R57" s="23"/>
       <c r="S57" s="23"/>
       <c r="T57" s="23"/>
       <c r="U57" s="26">
         <f>IF(I57=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" s="23">
         <f>IF(J57=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" s="23">
         <f>IF(K57=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="23">
         <f>IF(L57=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="23">
         <f>IF(M57=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z57" s="23">
         <f>IF(N57=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA57" s="23">
         <f>IF(O57=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB57" s="23">
         <f>IF(P57=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9855,7 +9873,7 @@
     </row>
     <row r="58" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B58" s="28" t="s">
         <v>46</v>
@@ -9871,7 +9889,7 @@
       </c>
       <c r="F58" s="32">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G58" s="29">
         <f t="shared" si="1"/>
@@ -9879,7 +9897,7 @@
       </c>
       <c r="H58" s="33">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I58" s="32">
         <v>2</v>
@@ -9896,15 +9914,9 @@
       <c r="M58" s="29">
         <v>2</v>
       </c>
-      <c r="N58" s="29">
-        <v>3</v>
-      </c>
-      <c r="O58" s="29">
-        <v>4</v>
-      </c>
-      <c r="P58" s="29">
-        <v>3</v>
-      </c>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
       <c r="Q58" s="32"/>
       <c r="R58" s="29"/>
       <c r="S58" s="29"/>
@@ -9931,7 +9943,7 @@
       </c>
       <c r="Z58" s="29">
         <f>IF(N58=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="29">
         <f>IF(O58=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -9939,12 +9951,12 @@
       </c>
       <c r="AB58" s="29">
         <f>IF(P58=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B59" s="22" t="s">
         <v>46</v>
@@ -9956,11 +9968,11 @@
         <v>0</v>
       </c>
       <c r="E59" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="26">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G59" s="23">
         <f t="shared" si="1"/>
@@ -9968,28 +9980,28 @@
       </c>
       <c r="H59" s="27">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="I59" s="26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59" s="23">
+        <v>2</v>
+      </c>
+      <c r="K59" s="23">
+        <v>3</v>
+      </c>
+      <c r="L59" s="23">
+        <v>3</v>
+      </c>
+      <c r="M59" s="23">
+        <v>2</v>
+      </c>
+      <c r="N59" s="23">
+        <v>3</v>
+      </c>
+      <c r="O59" s="23">
         <v>4</v>
-      </c>
-      <c r="K59" s="23">
-        <v>3</v>
-      </c>
-      <c r="L59" s="23">
-        <v>1</v>
-      </c>
-      <c r="M59" s="23">
-        <v>2</v>
-      </c>
-      <c r="N59" s="23">
-        <v>3</v>
-      </c>
-      <c r="O59" s="23">
-        <v>3</v>
       </c>
       <c r="P59" s="23">
         <v>3</v>
@@ -10000,11 +10012,11 @@
       <c r="T59" s="23"/>
       <c r="U59" s="26">
         <f>IF(I59=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" s="23">
         <f>IF(J59=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="23">
         <f>IF(K59=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10012,7 +10024,7 @@
       </c>
       <c r="X59" s="23">
         <f>IF(L59=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y59" s="23">
         <f>IF(M59=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10024,7 +10036,7 @@
       </c>
       <c r="AA59" s="23">
         <f>IF(O59=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="23">
         <f>IF(P59=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10033,7 +10045,7 @@
     </row>
     <row r="60" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B60" s="28" t="s">
         <v>46</v>
@@ -10045,11 +10057,11 @@
         <v>0</v>
       </c>
       <c r="E60" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="32">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G60" s="29">
         <f t="shared" si="1"/>
@@ -10057,19 +10069,19 @@
       </c>
       <c r="H60" s="33">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I60" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K60" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L60" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M60" s="29">
         <v>2</v>
@@ -10078,10 +10090,10 @@
         <v>3</v>
       </c>
       <c r="O60" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P60" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q60" s="32"/>
       <c r="R60" s="29"/>
@@ -10089,19 +10101,19 @@
       <c r="T60" s="29"/>
       <c r="U60" s="32">
         <f>IF(I60=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V60" s="29">
         <f>IF(J60=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W60" s="29">
         <f>IF(K60=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X60" s="29">
         <f>IF(L60=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="29">
         <f>IF(M60=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10113,16 +10125,16 @@
       </c>
       <c r="AA60" s="29">
         <f>IF(O60=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB60" s="29">
         <f>IF(P60=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B61" s="22" t="s">
         <v>46</v>
@@ -10138,7 +10150,7 @@
       </c>
       <c r="F61" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G61" s="23">
         <f t="shared" si="1"/>
@@ -10146,7 +10158,7 @@
       </c>
       <c r="H61" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="I61" s="26">
         <v>2</v>
@@ -10167,10 +10179,10 @@
         <v>3</v>
       </c>
       <c r="O61" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P61" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="26"/>
       <c r="R61" s="23"/>
@@ -10206,12 +10218,12 @@
       </c>
       <c r="AB61" s="23">
         <f>IF(P61=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B62" s="28" t="s">
         <v>46</v>
@@ -10227,7 +10239,7 @@
       </c>
       <c r="F62" s="32">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G62" s="29">
         <f t="shared" si="1"/>
@@ -10235,16 +10247,16 @@
       </c>
       <c r="H62" s="33">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I62" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" s="29">
         <v>2</v>
       </c>
       <c r="K62" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L62" s="29">
         <v>3</v>
@@ -10256,10 +10268,10 @@
         <v>3</v>
       </c>
       <c r="O62" s="29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P62" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q62" s="32"/>
       <c r="R62" s="29"/>
@@ -10267,7 +10279,7 @@
       <c r="T62" s="29"/>
       <c r="U62" s="32">
         <f>IF(I62=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V62" s="29">
         <f>IF(J62=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10275,7 +10287,7 @@
       </c>
       <c r="W62" s="29">
         <f>IF(K62=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="29">
         <f>IF(L62=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10295,12 +10307,12 @@
       </c>
       <c r="AB62" s="29">
         <f>IF(P62=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B63" s="22" t="s">
         <v>46</v>
@@ -10316,7 +10328,7 @@
       </c>
       <c r="F63" s="26">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G63" s="23">
         <f t="shared" si="1"/>
@@ -10324,7 +10336,7 @@
       </c>
       <c r="H63" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I63" s="26">
         <v>1</v>
@@ -10333,7 +10345,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63" s="23">
         <v>3</v>
@@ -10345,10 +10357,10 @@
         <v>3</v>
       </c>
       <c r="O63" s="23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P63" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q63" s="26"/>
       <c r="R63" s="23"/>
@@ -10364,7 +10376,7 @@
       </c>
       <c r="W63" s="23">
         <f>IF(K63=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X63" s="23">
         <f>IF(L63=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10384,12 +10396,12 @@
       </c>
       <c r="AB63" s="23">
         <f>IF(P63=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B64" s="28" t="s">
         <v>46</v>
@@ -10416,7 +10428,7 @@
         <v>0.5</v>
       </c>
       <c r="I64" s="32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J64" s="29">
         <v>2</v>
@@ -10425,7 +10437,7 @@
         <v>1</v>
       </c>
       <c r="L64" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M64" s="29">
         <v>2</v>
@@ -10434,7 +10446,7 @@
         <v>3</v>
       </c>
       <c r="O64" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P64" s="29">
         <v>3</v>
@@ -10457,7 +10469,7 @@
       </c>
       <c r="X64" s="29">
         <f>IF(L64=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64" s="29">
         <f>IF(M64=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10469,7 +10481,7 @@
       </c>
       <c r="AA64" s="29">
         <f>IF(O64=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB64" s="29">
         <f>IF(P64=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10478,7 +10490,7 @@
     </row>
     <row r="65" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B65" s="22" t="s">
         <v>46</v>
@@ -10494,7 +10506,7 @@
       </c>
       <c r="F65" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G65" s="23">
         <f t="shared" si="1"/>
@@ -10502,10 +10514,10 @@
       </c>
       <c r="H65" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="I65" s="26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J65" s="23">
         <v>2</v>
@@ -10514,7 +10526,7 @@
         <v>1</v>
       </c>
       <c r="L65" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M65" s="23">
         <v>2</v>
@@ -10523,7 +10535,7 @@
         <v>3</v>
       </c>
       <c r="O65" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P65" s="23">
         <v>3</v>
@@ -10534,7 +10546,7 @@
       <c r="T65" s="23"/>
       <c r="U65" s="26">
         <f>IF(I65=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V65" s="23">
         <f>IF(J65=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10546,7 +10558,7 @@
       </c>
       <c r="X65" s="23">
         <f>IF(L65=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y65" s="23">
         <f>IF(M65=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10558,7 +10570,7 @@
       </c>
       <c r="AA65" s="23">
         <f>IF(O65=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB65" s="23">
         <f>IF(P65=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10567,7 +10579,7 @@
     </row>
     <row r="66" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B66" s="28" t="s">
         <v>46</v>
@@ -10583,7 +10595,7 @@
       </c>
       <c r="F66" s="32">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G66" s="29">
         <f t="shared" si="1"/>
@@ -10591,7 +10603,7 @@
       </c>
       <c r="H66" s="33">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I66" s="32">
         <v>2</v>
@@ -10612,7 +10624,7 @@
         <v>3</v>
       </c>
       <c r="O66" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P66" s="29">
         <v>3</v>
@@ -10647,7 +10659,7 @@
       </c>
       <c r="AA66" s="29">
         <f>IF(O66=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB66" s="29">
         <f>IF(P66=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10656,7 +10668,7 @@
     </row>
     <row r="67" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B67" s="22" t="s">
         <v>46</v>
@@ -10672,7 +10684,7 @@
       </c>
       <c r="F67" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G67" s="23">
         <f t="shared" si="1"/>
@@ -10680,7 +10692,7 @@
       </c>
       <c r="H67" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I67" s="26">
         <v>2</v>
@@ -10704,7 +10716,7 @@
         <v>3</v>
       </c>
       <c r="P67" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q67" s="26"/>
       <c r="R67" s="23"/>
@@ -10740,12 +10752,12 @@
       </c>
       <c r="AB67" s="23">
         <f>IF(P67=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B68" s="28" t="s">
         <v>46</v>
@@ -10761,7 +10773,7 @@
       </c>
       <c r="F68" s="32">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G68" s="29">
         <f t="shared" si="1"/>
@@ -10769,31 +10781,31 @@
       </c>
       <c r="H68" s="33">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I68" s="32">
+        <v>2</v>
+      </c>
+      <c r="J68" s="29">
+        <v>2</v>
+      </c>
+      <c r="K68" s="29">
+        <v>1</v>
+      </c>
+      <c r="L68" s="29">
+        <v>3</v>
+      </c>
+      <c r="M68" s="29">
+        <v>2</v>
+      </c>
+      <c r="N68" s="29">
+        <v>3</v>
+      </c>
+      <c r="O68" s="29">
+        <v>3</v>
+      </c>
+      <c r="P68" s="29">
         <v>4</v>
-      </c>
-      <c r="J68" s="29">
-        <v>2</v>
-      </c>
-      <c r="K68" s="29">
-        <v>3</v>
-      </c>
-      <c r="L68" s="29">
-        <v>1</v>
-      </c>
-      <c r="M68" s="29">
-        <v>2</v>
-      </c>
-      <c r="N68" s="29">
-        <v>3</v>
-      </c>
-      <c r="O68" s="29">
-        <v>2</v>
-      </c>
-      <c r="P68" s="29">
-        <v>3</v>
       </c>
       <c r="Q68" s="32"/>
       <c r="R68" s="29"/>
@@ -10801,7 +10813,7 @@
       <c r="T68" s="29"/>
       <c r="U68" s="32">
         <f>IF(I68=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V68" s="29">
         <f>IF(J68=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10809,11 +10821,11 @@
       </c>
       <c r="W68" s="29">
         <f>IF(K68=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X68" s="29">
         <f>IF(L68=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y68" s="29">
         <f>IF(M68=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10825,16 +10837,16 @@
       </c>
       <c r="AA68" s="29">
         <f>IF(O68=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB68" s="29">
         <f>IF(P68=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B69" s="22" t="s">
         <v>46</v>
@@ -10843,14 +10855,14 @@
         <v>4</v>
       </c>
       <c r="D69" s="24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="25" t="b">
         <v>0</v>
       </c>
       <c r="F69" s="26">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G69" s="23">
         <f t="shared" si="1"/>
@@ -10858,19 +10870,19 @@
       </c>
       <c r="H69" s="27">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I69" s="26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" s="23">
         <v>2</v>
       </c>
       <c r="K69" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L69" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M69" s="23">
         <v>2</v>
@@ -10879,7 +10891,7 @@
         <v>3</v>
       </c>
       <c r="O69" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P69" s="23">
         <v>3</v>
@@ -10890,7 +10902,7 @@
       <c r="T69" s="23"/>
       <c r="U69" s="26">
         <f>IF(I69=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V69" s="23">
         <f>IF(J69=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10898,11 +10910,11 @@
       </c>
       <c r="W69" s="23">
         <f>IF(K69=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X69" s="23">
         <f>IF(L69=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y69" s="23">
         <f>IF(M69=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10914,7 +10926,7 @@
       </c>
       <c r="AA69" s="23">
         <f>IF(O69=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB69" s="23">
         <f>IF(P69=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -10923,7 +10935,7 @@
     </row>
     <row r="70" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B70" s="28" t="s">
         <v>46</v>
@@ -10932,7 +10944,7 @@
         <v>4</v>
       </c>
       <c r="D70" s="30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="31" t="b">
         <v>0</v>
@@ -11012,7 +11024,7 @@
     </row>
     <row r="71" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B71" s="22" t="s">
         <v>46</v>
@@ -11024,11 +11036,11 @@
         <v>0</v>
       </c>
       <c r="E71" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G71" s="23">
         <f t="shared" si="1"/>
@@ -11036,7 +11048,7 @@
       </c>
       <c r="H71" s="27">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I71" s="26">
         <v>2</v>
@@ -11045,19 +11057,19 @@
         <v>2</v>
       </c>
       <c r="K71" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L71" s="23">
         <v>3</v>
       </c>
       <c r="M71" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N71" s="23">
         <v>3</v>
       </c>
       <c r="O71" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P71" s="23">
         <v>3</v>
@@ -11076,7 +11088,7 @@
       </c>
       <c r="W71" s="23">
         <f>IF(K71=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="23">
         <f>IF(L71=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11084,7 +11096,7 @@
       </c>
       <c r="Y71" s="23">
         <f>IF(M71=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z71" s="23">
         <f>IF(N71=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11092,7 +11104,7 @@
       </c>
       <c r="AA71" s="23">
         <f>IF(O71=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB71" s="23">
         <f>IF(P71=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11101,7 +11113,7 @@
     </row>
     <row r="72" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B72" s="28" t="s">
         <v>46</v>
@@ -11113,11 +11125,11 @@
         <v>0</v>
       </c>
       <c r="E72" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="32">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G72" s="29">
         <f t="shared" si="1"/>
@@ -11125,31 +11137,31 @@
       </c>
       <c r="H72" s="33">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I72" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" s="29">
         <v>2</v>
       </c>
       <c r="K72" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L72" s="29">
         <v>3</v>
       </c>
       <c r="M72" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" s="29">
         <v>3</v>
       </c>
       <c r="O72" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P72" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q72" s="32"/>
       <c r="R72" s="29"/>
@@ -11157,7 +11169,7 @@
       <c r="T72" s="29"/>
       <c r="U72" s="32">
         <f>IF(I72=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V72" s="29">
         <f>IF(J72=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11173,7 +11185,7 @@
       </c>
       <c r="Y72" s="29">
         <f>IF(M72=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z72" s="29">
         <f>IF(N72=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11185,12 +11197,12 @@
       </c>
       <c r="AB72" s="29">
         <f>IF(P72=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B73" s="22" t="s">
         <v>46</v>
@@ -11206,7 +11218,7 @@
       </c>
       <c r="F73" s="26">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G73" s="23">
         <f t="shared" si="1"/>
@@ -11214,16 +11226,16 @@
       </c>
       <c r="H73" s="27">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I73" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73" s="23">
         <v>2</v>
       </c>
       <c r="K73" s="23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L73" s="23">
         <v>3</v>
@@ -11235,10 +11247,10 @@
         <v>3</v>
       </c>
       <c r="O73" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P73" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q73" s="26"/>
       <c r="R73" s="23"/>
@@ -11246,7 +11258,7 @@
       <c r="T73" s="23"/>
       <c r="U73" s="26">
         <f>IF(I73=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" s="23">
         <f>IF(J73=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11254,7 +11266,7 @@
       </c>
       <c r="W73" s="23">
         <f>IF(K73=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X73" s="23">
         <f>IF(L73=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11270,16 +11282,16 @@
       </c>
       <c r="AA73" s="23">
         <f>IF(O73=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB73" s="23">
         <f>IF(P73=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B74" s="28" t="s">
         <v>46</v>
@@ -11295,7 +11307,7 @@
       </c>
       <c r="F74" s="32">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G74" s="29">
         <f t="shared" si="1"/>
@@ -11303,7 +11315,7 @@
       </c>
       <c r="H74" s="33">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I74" s="32">
         <v>2</v>
@@ -11312,7 +11324,7 @@
         <v>2</v>
       </c>
       <c r="K74" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L74" s="29">
         <v>3</v>
@@ -11324,10 +11336,10 @@
         <v>3</v>
       </c>
       <c r="O74" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P74" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q74" s="32"/>
       <c r="R74" s="29"/>
@@ -11343,7 +11355,7 @@
       </c>
       <c r="W74" s="29">
         <f>IF(K74=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X74" s="29">
         <f>IF(L74=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11359,16 +11371,16 @@
       </c>
       <c r="AA74" s="29">
         <f>IF(O74=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB74" s="29">
         <f>IF(P74=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B75" s="22" t="s">
         <v>46</v>
@@ -11384,7 +11396,7 @@
       </c>
       <c r="F75" s="26">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G75" s="23">
         <f t="shared" si="1"/>
@@ -11392,7 +11404,7 @@
       </c>
       <c r="H75" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I75" s="26">
         <v>2</v>
@@ -11401,10 +11413,10 @@
         <v>2</v>
       </c>
       <c r="K75" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L75" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M75" s="23">
         <v>2</v>
@@ -11413,10 +11425,10 @@
         <v>3</v>
       </c>
       <c r="O75" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P75" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q75" s="26"/>
       <c r="R75" s="23"/>
@@ -11432,11 +11444,11 @@
       </c>
       <c r="W75" s="23">
         <f>IF(K75=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X75" s="23">
         <f>IF(L75=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y75" s="23">
         <f>IF(M75=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11452,12 +11464,12 @@
       </c>
       <c r="AB75" s="23">
         <f>IF(P75=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B76" s="28" t="s">
         <v>46</v>
@@ -11473,7 +11485,7 @@
       </c>
       <c r="F76" s="32">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G76" s="29">
         <f t="shared" si="1"/>
@@ -11481,7 +11493,7 @@
       </c>
       <c r="H76" s="33">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="I76" s="32">
         <v>2</v>
@@ -11493,16 +11505,20 @@
         <v>1</v>
       </c>
       <c r="L76" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M76" s="29">
         <v>2</v>
       </c>
       <c r="N76" s="29">
+        <v>3</v>
+      </c>
+      <c r="O76" s="29">
         <v>4</v>
       </c>
-      <c r="O76" s="29"/>
-      <c r="P76" s="29"/>
+      <c r="P76" s="29">
+        <v>3</v>
+      </c>
       <c r="Q76" s="32"/>
       <c r="R76" s="29"/>
       <c r="S76" s="29"/>
@@ -11521,7 +11537,7 @@
       </c>
       <c r="X76" s="29">
         <f>IF(L76=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y76" s="29">
         <f>IF(M76=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11529,7 +11545,7 @@
       </c>
       <c r="Z76" s="29">
         <f>IF(N76=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA76" s="29">
         <f>IF(O76=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11537,12 +11553,12 @@
       </c>
       <c r="AB76" s="29">
         <f>IF(P76=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B77" s="22" t="s">
         <v>46</v>
@@ -11558,7 +11574,7 @@
       </c>
       <c r="F77" s="26">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G77" s="23">
         <f t="shared" si="1"/>
@@ -11566,39 +11582,35 @@
       </c>
       <c r="H77" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I77" s="26">
+        <v>2</v>
+      </c>
+      <c r="J77" s="23">
+        <v>2</v>
+      </c>
+      <c r="K77" s="23">
+        <v>1</v>
+      </c>
+      <c r="L77" s="23">
+        <v>3</v>
+      </c>
+      <c r="M77" s="23">
+        <v>2</v>
+      </c>
+      <c r="N77" s="23">
         <v>4</v>
       </c>
-      <c r="J77" s="23">
-        <v>2</v>
-      </c>
-      <c r="K77" s="23">
-        <v>4</v>
-      </c>
-      <c r="L77" s="23">
-        <v>3</v>
-      </c>
-      <c r="M77" s="23">
-        <v>2</v>
-      </c>
-      <c r="N77" s="23">
-        <v>3</v>
-      </c>
-      <c r="O77" s="23">
-        <v>3</v>
-      </c>
-      <c r="P77" s="23">
-        <v>3</v>
-      </c>
+      <c r="O77" s="23"/>
+      <c r="P77" s="23"/>
       <c r="Q77" s="26"/>
       <c r="R77" s="23"/>
       <c r="S77" s="23"/>
       <c r="T77" s="23"/>
       <c r="U77" s="26">
         <f>IF(I77=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V77" s="23">
         <f>IF(J77=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11606,7 +11618,7 @@
       </c>
       <c r="W77" s="23">
         <f>IF(K77=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X77" s="23">
         <f>IF(L77=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11618,20 +11630,20 @@
       </c>
       <c r="Z77" s="23">
         <f>IF(N77=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA77" s="23">
         <f>IF(O77=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB77" s="23">
         <f>IF(P77=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B78" s="28" t="s">
         <v>46</v>
@@ -11643,11 +11655,11 @@
         <v>0</v>
       </c>
       <c r="E78" s="31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" s="32">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G78" s="29">
         <f t="shared" si="1"/>
@@ -11655,28 +11667,28 @@
       </c>
       <c r="H78" s="33">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I78" s="32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J78" s="29">
+        <v>2</v>
+      </c>
+      <c r="K78" s="29">
         <v>4</v>
       </c>
-      <c r="K78" s="29">
-        <v>3</v>
-      </c>
       <c r="L78" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M78" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N78" s="29">
         <v>3</v>
       </c>
       <c r="O78" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P78" s="29">
         <v>3</v>
@@ -11687,11 +11699,11 @@
       <c r="T78" s="29"/>
       <c r="U78" s="32">
         <f>IF(I78=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V78" s="29">
         <f>IF(J78=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="29">
         <f>IF(K78=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11699,11 +11711,11 @@
       </c>
       <c r="X78" s="29">
         <f>IF(L78=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y78" s="29">
         <f>IF(M78=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z78" s="29">
         <f>IF(N78=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11711,7 +11723,7 @@
       </c>
       <c r="AA78" s="29">
         <f>IF(O78=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB78" s="29">
         <f>IF(P78=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11720,7 +11732,7 @@
     </row>
     <row r="79" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B79" s="22" t="s">
         <v>46</v>
@@ -11732,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="26">
         <f t="shared" si="0"/>
@@ -11753,22 +11765,22 @@
         <v>4</v>
       </c>
       <c r="K79" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L79" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M79" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N79" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O79" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P79" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q79" s="26"/>
       <c r="R79" s="23"/>
@@ -11784,7 +11796,7 @@
       </c>
       <c r="W79" s="23">
         <f>IF(K79=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X79" s="23">
         <f>IF(L79=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11796,20 +11808,20 @@
       </c>
       <c r="Z79" s="23">
         <f>IF(N79=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA79" s="23">
         <f>IF(O79=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB79" s="23">
         <f>IF(P79=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B80" s="28" t="s">
         <v>46</v>
@@ -11825,7 +11837,7 @@
       </c>
       <c r="F80" s="32">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G80" s="29">
         <f t="shared" si="1"/>
@@ -11833,31 +11845,31 @@
       </c>
       <c r="H80" s="33">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.25</v>
       </c>
       <c r="I80" s="32">
         <v>2</v>
       </c>
       <c r="J80" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K80" s="29">
         <v>1</v>
       </c>
       <c r="L80" s="29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N80" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O80" s="29">
         <v>3</v>
       </c>
       <c r="P80" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="32"/>
       <c r="R80" s="29"/>
@@ -11869,7 +11881,7 @@
       </c>
       <c r="V80" s="29">
         <f>IF(J80=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W80" s="29">
         <f>IF(K80=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11877,15 +11889,15 @@
       </c>
       <c r="X80" s="29">
         <f>IF(L80=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y80" s="29">
         <f>IF(M80=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z80" s="29">
         <f>IF(N80=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA80" s="29">
         <f>IF(O80=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11893,12 +11905,12 @@
       </c>
       <c r="AB80" s="29">
         <f>IF(P80=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B81" s="22" t="s">
         <v>46</v>
@@ -11910,11 +11922,11 @@
         <v>0</v>
       </c>
       <c r="E81" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" s="26">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G81" s="23">
         <f t="shared" si="1"/>
@@ -11922,16 +11934,16 @@
       </c>
       <c r="H81" s="27">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I81" s="26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J81" s="23">
         <v>2</v>
       </c>
       <c r="K81" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L81" s="23">
         <v>3</v>
@@ -11943,10 +11955,10 @@
         <v>3</v>
       </c>
       <c r="O81" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P81" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q81" s="26"/>
       <c r="R81" s="23"/>
@@ -11954,7 +11966,7 @@
       <c r="T81" s="23"/>
       <c r="U81" s="26">
         <f>IF(I81=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" s="23">
         <f>IF(J81=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11962,7 +11974,7 @@
       </c>
       <c r="W81" s="23">
         <f>IF(K81=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X81" s="23">
         <f>IF(L81=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -11978,16 +11990,16 @@
       </c>
       <c r="AA81" s="23">
         <f>IF(O81=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB81" s="23">
         <f>IF(P81=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B82" s="34" t="s">
         <v>46</v>
@@ -12014,28 +12026,28 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="I82" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J82" s="35">
+        <v>2</v>
+      </c>
+      <c r="K82" s="35">
         <v>4</v>
       </c>
-      <c r="K82" s="35">
-        <v>1</v>
-      </c>
       <c r="L82" s="35">
         <v>3</v>
       </c>
       <c r="M82" s="35">
+        <v>2</v>
+      </c>
+      <c r="N82" s="35">
+        <v>3</v>
+      </c>
+      <c r="O82" s="35">
+        <v>1</v>
+      </c>
+      <c r="P82" s="35">
         <v>4</v>
-      </c>
-      <c r="N82" s="35">
-        <v>2</v>
-      </c>
-      <c r="O82" s="35">
-        <v>3</v>
-      </c>
-      <c r="P82" s="35">
-        <v>2</v>
       </c>
       <c r="Q82" s="38"/>
       <c r="R82" s="35"/>
@@ -12043,15 +12055,15 @@
       <c r="T82" s="35"/>
       <c r="U82" s="38">
         <f>IF(I82=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V82" s="35">
         <f>IF(J82=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="35">
         <f>IF(K82=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X82" s="35">
         <f>IF(L82=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
@@ -12059,32 +12071,121 @@
       </c>
       <c r="Y82" s="35">
         <f>IF(M82=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z82" s="35">
         <f>IF(N82=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA82" s="35">
         <f>IF(O82=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB82" s="35">
         <f>IF(P82=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="83" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="10" t="s">
+        <v>855</v>
+      </c>
+      <c r="B83" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" s="29">
+        <v>4</v>
+      </c>
+      <c r="D83" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" s="32">
+        <f>SUM(U83:AB83)</f>
+        <v>4</v>
+      </c>
+      <c r="G83" s="29">
+        <f>SUM(Q83:T83)</f>
+        <v>0</v>
+      </c>
+      <c r="H83" s="33">
+        <f>SUM(F83:G83)/12</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I83" s="32">
+        <v>2</v>
+      </c>
+      <c r="J83" s="29">
+        <v>4</v>
+      </c>
+      <c r="K83" s="29">
+        <v>1</v>
+      </c>
+      <c r="L83" s="29">
+        <v>3</v>
+      </c>
+      <c r="M83" s="29">
+        <v>4</v>
+      </c>
+      <c r="N83" s="29">
+        <v>2</v>
+      </c>
+      <c r="O83" s="29">
+        <v>3</v>
+      </c>
+      <c r="P83" s="29">
+        <v>2</v>
+      </c>
+      <c r="Q83" s="32"/>
+      <c r="R83" s="29"/>
+      <c r="S83" s="29"/>
+      <c r="T83" s="29"/>
+      <c r="U83" s="32">
+        <f>IF(I83=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V83" s="29">
+        <f>IF(J83=VLOOKUP(VALUE(J$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W83" s="29">
+        <f>IF(K83=VLOOKUP(VALUE(K$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X83" s="29">
+        <f>IF(L83=VLOOKUP(VALUE(L$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y83" s="29">
+        <f>IF(M83=VLOOKUP(VALUE(M$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z83" s="29">
+        <f>IF(N83=VLOOKUP(VALUE(N$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA83" s="29">
+        <f>IF(O83=VLOOKUP(VALUE(O$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB83" s="29">
+        <f>IF(P83=VLOOKUP(VALUE(P$1),Questions[#All],5,FALSE),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:P82">
+  <conditionalFormatting sqref="I2:P83">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>U2=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B82" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B83" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Dushin,Sourial"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:H82" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:H83" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -12217,12 +12318,12 @@
         <v>720</v>
       </c>
       <c r="P2" s="6">
-        <f>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</f>
-        <v>0.64197530864197527</v>
+        <f>AVERAGE(INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]))</f>
+        <v>0.63414634146341464</v>
       </c>
       <c r="Q2" s="7" cm="1">
-        <f t="array" ref="Q2">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</f>
-        <v>0.40059982104646302</v>
+        <f t="array" ref="Q2">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$83-_xlpm.item))</f>
+        <v>0.41101053695510936</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -12272,12 +12373,12 @@
         <v>720</v>
       </c>
       <c r="P3" s="6">
-        <f>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</f>
-        <v>0.81481481481481477</v>
+        <f>AVERAGE(INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]))</f>
+        <v>0.80487804878048785</v>
       </c>
       <c r="Q3" s="7" cm="1">
-        <f t="array" ref="Q3">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</f>
-        <v>0.23810932312496966</v>
+        <f t="array" ref="Q3">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$83-_xlpm.item))</f>
+        <v>0.25393241364443253</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -12327,12 +12428,12 @@
         <v>720</v>
       </c>
       <c r="P4" s="6">
-        <f>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</f>
-        <v>0.59259259259259256</v>
+        <f>AVERAGE(INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]))</f>
+        <v>0.58536585365853655</v>
       </c>
       <c r="Q4" s="7" cm="1">
-        <f t="array" ref="Q4">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</f>
-        <v>0.28398455912630444</v>
+        <f t="array" ref="Q4">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$83-_xlpm.item))</f>
+        <v>0.29533711195683582</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -12382,12 +12483,12 @@
         <v>739</v>
       </c>
       <c r="P5" s="6">
-        <f>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</f>
-        <v>0.71604938271604934</v>
+        <f>AVERAGE(INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]))</f>
+        <v>0.70731707317073167</v>
       </c>
       <c r="Q5" s="7" cm="1">
-        <f t="array" ref="Q5">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</f>
-        <v>0.42338067987099925</v>
+        <f t="array" ref="Q5">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$83-_xlpm.item))</f>
+        <v>0.43412950872797323</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -12437,12 +12538,12 @@
         <v>746</v>
       </c>
       <c r="P6" s="6">
-        <f>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</f>
-        <v>0.79012345679012341</v>
+        <f>AVERAGE(INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]))</f>
+        <v>0.79268292682926833</v>
       </c>
       <c r="Q6" s="7" cm="1">
-        <f t="array" ref="Q6">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</f>
-        <v>0.6229701963155303</v>
+        <f t="array" ref="Q6">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$83-_xlpm.item))</f>
+        <v>0.60209401937655405</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -12492,12 +12593,12 @@
         <v>754</v>
       </c>
       <c r="P7" s="6">
-        <f>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</f>
-        <v>0.72839506172839508</v>
+        <f>AVERAGE(INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]))</f>
+        <v>0.71951219512195119</v>
       </c>
       <c r="Q7" s="7" cm="1">
-        <f t="array" ref="Q7">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</f>
-        <v>0.39200433954708791</v>
+        <f t="array" ref="Q7">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$83-_xlpm.item))</f>
+        <v>0.40342462428114018</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -12547,12 +12648,12 @@
         <v>761</v>
       </c>
       <c r="P8" s="6">
-        <f>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</f>
-        <v>0.58024691358024694</v>
+        <f>AVERAGE(INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]))</f>
+        <v>0.58536585365853655</v>
       </c>
       <c r="Q8" s="7" cm="1">
-        <f t="array" ref="Q8">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</f>
-        <v>0.14094467796619645</v>
+        <f t="array" ref="Q8">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$83-_xlpm.item))</f>
+        <v>0.12178139108413341</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -12602,12 +12703,12 @@
         <v>761</v>
       </c>
       <c r="P9" s="6">
-        <f>AVERAGE(INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]))</f>
-        <v>0.66666666666666663</v>
+        <f>AVERAGE(INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]))</f>
+        <v>0.67073170731707321</v>
       </c>
       <c r="Q9" s="7" cm="1">
-        <f t="array" ref="Q9">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$82,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$82-_xlpm.item))</f>
-        <v>0.31706488201475336</v>
+        <f t="array" ref="Q9">_xlfn.LET(_xlpm.item,INDEX(Scores!$U$2:$AB$83,0,Questions[[#This Row],['#]]),CORREL(_xlpm.item,Scores!$F$2:$F$83-_xlpm.item))</f>
+        <v>0.29737579460386337</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">

--- a/Global/October CMA/Global October CMA Data.xlsx
+++ b/Global/October CMA/Global October CMA Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coledushin/Documents/GWHS/Global/October CMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309707F9-1A71-894C-A93D-A1887A033B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6383A0A2-1D17-3D4E-97A8-AF1CFB6162C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="858">
   <si>
     <t>Model</t>
   </si>
@@ -2666,6 +2666,9 @@
   </si>
   <si>
     <t>FAL91039</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -3062,17 +3065,42 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{E24C90E3-2734-B149-B611-0E6AC5E040E3}"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="59">
     <dxf>
       <font>
-        <color rgb="FFBB463C"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFD9D6"/>
-          <bgColor rgb="FFFFD9D6"/>
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF5F8FB"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="hair">
+          <color rgb="FFECF0F4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3817,42 +3845,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF5F8FB"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="hair">
-          <color rgb="FFECF0F4"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -4383,40 +4375,40 @@
   </dxfs>
   <tableStyles count="6">
     <tableStyle name="Questions-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="59"/>
-      <tableStyleElement type="headerRow" dxfId="58"/>
-      <tableStyleElement type="firstRowStripe" dxfId="57"/>
-      <tableStyleElement type="secondRowStripe" dxfId="56"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="58"/>
+      <tableStyleElement type="headerRow" dxfId="57"/>
+      <tableStyleElement type="firstRowStripe" dxfId="56"/>
+      <tableStyleElement type="secondRowStripe" dxfId="55"/>
     </tableStyle>
     <tableStyle name="Task Models-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="55"/>
-      <tableStyleElement type="headerRow" dxfId="54"/>
-      <tableStyleElement type="firstRowStripe" dxfId="53"/>
-      <tableStyleElement type="secondRowStripe" dxfId="52"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="54"/>
+      <tableStyleElement type="headerRow" dxfId="53"/>
+      <tableStyleElement type="firstRowStripe" dxfId="52"/>
+      <tableStyleElement type="secondRowStripe" dxfId="51"/>
     </tableStyle>
     <tableStyle name="Scores-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="51"/>
-      <tableStyleElement type="headerRow" dxfId="50"/>
-      <tableStyleElement type="firstRowStripe" dxfId="49"/>
-      <tableStyleElement type="secondRowStripe" dxfId="48"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="50"/>
+      <tableStyleElement type="headerRow" dxfId="49"/>
+      <tableStyleElement type="firstRowStripe" dxfId="48"/>
+      <tableStyleElement type="secondRowStripe" dxfId="47"/>
     </tableStyle>
     <tableStyle name="Skill Standards-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="47"/>
-      <tableStyleElement type="headerRow" dxfId="46"/>
-      <tableStyleElement type="firstRowStripe" dxfId="45"/>
-      <tableStyleElement type="secondRowStripe" dxfId="44"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="46"/>
+      <tableStyleElement type="headerRow" dxfId="45"/>
+      <tableStyleElement type="firstRowStripe" dxfId="44"/>
+      <tableStyleElement type="secondRowStripe" dxfId="43"/>
     </tableStyle>
     <tableStyle name="Content Standards-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="43"/>
-      <tableStyleElement type="headerRow" dxfId="42"/>
-      <tableStyleElement type="firstRowStripe" dxfId="41"/>
-      <tableStyleElement type="secondRowStripe" dxfId="40"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="42"/>
+      <tableStyleElement type="headerRow" dxfId="41"/>
+      <tableStyleElement type="firstRowStripe" dxfId="40"/>
+      <tableStyleElement type="secondRowStripe" dxfId="39"/>
     </tableStyle>
     <tableStyle name="Light and Airy" count="4" xr9:uid="{D3C6459B-EC7F-4F41-B005-22E80AE40871}">
-      <tableStyleElement type="wholeTable" dxfId="39"/>
-      <tableStyleElement type="headerRow" dxfId="38"/>
-      <tableStyleElement type="totalRow" dxfId="37"/>
-      <tableStyleElement type="firstRowStripe" dxfId="36"/>
+      <tableStyleElement type="wholeTable" dxfId="38"/>
+      <tableStyleElement type="headerRow" dxfId="37"/>
+      <tableStyleElement type="totalRow" dxfId="36"/>
+      <tableStyleElement type="firstRowStripe" dxfId="35"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4453,22 +4445,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}" name="Scores" displayName="Scores" ref="A1:AB83" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" tableBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}" name="Scores" displayName="Scores" ref="A1:AB83" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
   <autoFilter ref="A1:AB83" xr:uid="{0FB7B861-B9F2-C349-9CEE-8CA337C06ED3}"/>
   <tableColumns count="28">
-    <tableColumn id="1" xr3:uid="{BDA62A2B-B3CF-1C42-B26C-859C05903E15}" name="Key" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{B0B24296-AFCF-A649-81B0-797BEB307C4C}" name="Class" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{3E4EABAF-90C9-9E45-B32C-3EE0290EB454}" name="Period" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{C8AD8DDD-6CF2-B44B-9413-E525D4CC5073}" name="ELL" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{D7AFA008-A5EC-0A49-B514-792B12195C8D}" name="IEP" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{B389A40C-5893-DD4D-8A49-52AC9F46E8DC}" name="MC" dataDxfId="27">
+    <tableColumn id="1" xr3:uid="{BDA62A2B-B3CF-1C42-B26C-859C05903E15}" name="Key" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{B0B24296-AFCF-A649-81B0-797BEB307C4C}" name="Class" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{3E4EABAF-90C9-9E45-B32C-3EE0290EB454}" name="Period" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{C8AD8DDD-6CF2-B44B-9413-E525D4CC5073}" name="ELL" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{D7AFA008-A5EC-0A49-B514-792B12195C8D}" name="IEP" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{B389A40C-5893-DD4D-8A49-52AC9F46E8DC}" name="MC" dataDxfId="26">
       <calculatedColumnFormula>SUM(U2:AB2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6D925722-96DA-1749-A527-ACB45D97657F}" name="CRQ" dataDxfId="26">
+    <tableColumn id="7" xr3:uid="{6D925722-96DA-1749-A527-ACB45D97657F}" name="CRQ" dataDxfId="25">
       <calculatedColumnFormula>SUM(Q2:T2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D6CC8E81-E712-E74D-B287-58B154A14A59}" name="Final" dataDxfId="25">
-      <calculatedColumnFormula>SUM(F2:G2)/12</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{D6CC8E81-E712-E74D-B287-58B154A14A59}" name="Final" dataDxfId="0">
+      <calculatedColumnFormula>SUM(F2:G2)/24+0.5</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{D1D28B64-20BB-A248-9F60-F9562825ED9A}" name="1" dataDxfId="24"/>
     <tableColumn id="10" xr3:uid="{DD495C25-BB33-2345-91D2-F162C405127D}" name="2" dataDxfId="23"/>
@@ -4920,8 +4912,8 @@
         <v>0</v>
       </c>
       <c r="H2" s="21">
-        <f t="shared" ref="H2:H82" si="2">SUM(F2:G2)/12</f>
-        <v>0.66666666666666663</v>
+        <f t="shared" ref="H2:H33" si="2">SUM(F2:G2)/24+0.5</f>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I2" s="20">
         <v>2</v>
@@ -5010,7 +5002,7 @@
       </c>
       <c r="H3" s="27">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="I3" s="26">
         <v>2</v>
@@ -5099,7 +5091,7 @@
       </c>
       <c r="H4" s="33">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I4" s="32">
         <v>1</v>
@@ -5188,7 +5180,7 @@
       </c>
       <c r="H5" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I5" s="26">
         <v>1</v>
@@ -5277,7 +5269,7 @@
       </c>
       <c r="H6" s="33">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I6" s="32">
         <v>2</v>
@@ -5366,7 +5358,7 @@
       </c>
       <c r="H7" s="27">
         <f t="shared" si="2"/>
-        <v>0.16666666666666666</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I7" s="26">
         <v>4</v>
@@ -5453,7 +5445,7 @@
       </c>
       <c r="H8" s="33">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I8" s="32">
         <v>2</v>
@@ -5542,7 +5534,7 @@
       </c>
       <c r="H9" s="27">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I9" s="26">
         <v>2</v>
@@ -5630,8 +5622,8 @@
         <v>0</v>
       </c>
       <c r="H10" s="33">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <f>SUM(F10:G10)/24+0.5</f>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I10" s="32">
         <v>2</v>
@@ -5720,7 +5712,7 @@
       </c>
       <c r="H11" s="27">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="I11" s="26">
         <v>1</v>
@@ -5809,7 +5801,7 @@
       </c>
       <c r="H12" s="33">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="I12" s="32">
         <v>1</v>
@@ -5896,7 +5888,7 @@
       </c>
       <c r="H13" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I13" s="26">
         <v>2</v>
@@ -5985,7 +5977,7 @@
       </c>
       <c r="H14" s="33">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I14" s="32">
         <v>2</v>
@@ -6074,7 +6066,7 @@
       </c>
       <c r="H15" s="27">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I15" s="26">
         <v>2</v>
@@ -6163,7 +6155,7 @@
       </c>
       <c r="H16" s="33">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I16" s="32">
         <v>2</v>
@@ -6252,7 +6244,7 @@
       </c>
       <c r="H17" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I17" s="26">
         <v>2</v>
@@ -6341,7 +6333,7 @@
       </c>
       <c r="H18" s="33">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="I18" s="32">
         <v>3</v>
@@ -6430,7 +6422,7 @@
       </c>
       <c r="H19" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I19" s="26">
         <v>2</v>
@@ -6519,7 +6511,7 @@
       </c>
       <c r="H20" s="33">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I20" s="32">
         <v>1</v>
@@ -6604,11 +6596,11 @@
       </c>
       <c r="G21" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.91666666666666674</v>
       </c>
       <c r="I21" s="26">
         <v>2</v>
@@ -6634,10 +6626,18 @@
       <c r="P21" s="23">
         <v>3</v>
       </c>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
+      <c r="Q21" s="26">
+        <v>0</v>
+      </c>
+      <c r="R21" s="23">
+        <v>1</v>
+      </c>
+      <c r="S21" s="23">
+        <v>1</v>
+      </c>
+      <c r="T21" s="23">
+        <v>1</v>
+      </c>
       <c r="U21" s="26">
         <f>IF(I21=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -6693,11 +6693,11 @@
       </c>
       <c r="G22" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="33">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="I22" s="32">
         <v>2</v>
@@ -6723,10 +6723,18 @@
       <c r="P22" s="29">
         <v>4</v>
       </c>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
+      <c r="Q22" s="32">
+        <v>0</v>
+      </c>
+      <c r="R22" s="29">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29">
+        <v>1</v>
+      </c>
+      <c r="T22" s="29">
+        <v>1</v>
+      </c>
       <c r="U22" s="32">
         <f>IF(I22=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -6782,11 +6790,11 @@
       </c>
       <c r="G23" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="27">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I23" s="26">
         <v>2</v>
@@ -6812,10 +6820,18 @@
       <c r="P23" s="23">
         <v>3</v>
       </c>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
+      <c r="Q23" s="26">
+        <v>0</v>
+      </c>
+      <c r="R23" s="23">
+        <v>0</v>
+      </c>
+      <c r="S23" s="23">
+        <v>1</v>
+      </c>
+      <c r="T23" s="23">
+        <v>0</v>
+      </c>
       <c r="U23" s="26">
         <f>IF(I23=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -6875,7 +6891,7 @@
       </c>
       <c r="H24" s="33">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I24" s="32">
         <v>2</v>
@@ -6901,10 +6917,18 @@
       <c r="P24" s="29">
         <v>3</v>
       </c>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
+      <c r="Q24" s="32" t="s">
+        <v>857</v>
+      </c>
+      <c r="R24" s="29">
+        <v>0</v>
+      </c>
+      <c r="S24" s="29" t="s">
+        <v>857</v>
+      </c>
+      <c r="T24" s="29" t="s">
+        <v>857</v>
+      </c>
       <c r="U24" s="32">
         <f>IF(I24=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -6960,11 +6984,11 @@
       </c>
       <c r="G25" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" s="27">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.91666666666666674</v>
       </c>
       <c r="I25" s="26">
         <v>2</v>
@@ -6990,10 +7014,18 @@
       <c r="P25" s="23">
         <v>3</v>
       </c>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
+      <c r="Q25" s="26">
+        <v>0</v>
+      </c>
+      <c r="R25" s="23">
+        <v>0</v>
+      </c>
+      <c r="S25" s="23">
+        <v>1</v>
+      </c>
+      <c r="T25" s="23">
+        <v>1</v>
+      </c>
       <c r="U25" s="26">
         <f>IF(I25=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7049,11 +7081,11 @@
       </c>
       <c r="G26" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" s="33">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I26" s="32">
         <v>2</v>
@@ -7079,10 +7111,18 @@
       <c r="P26" s="29">
         <v>3</v>
       </c>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
+      <c r="Q26" s="32">
+        <v>0</v>
+      </c>
+      <c r="R26" s="29">
+        <v>0</v>
+      </c>
+      <c r="S26" s="29">
+        <v>1</v>
+      </c>
+      <c r="T26" s="29">
+        <v>1</v>
+      </c>
       <c r="U26" s="32">
         <f>IF(I26=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7138,11 +7178,11 @@
       </c>
       <c r="G27" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.91666666666666674</v>
       </c>
       <c r="I27" s="26">
         <v>2</v>
@@ -7168,10 +7208,18 @@
       <c r="P27" s="23">
         <v>3</v>
       </c>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
+      <c r="Q27" s="26">
+        <v>1</v>
+      </c>
+      <c r="R27" s="23">
+        <v>1</v>
+      </c>
+      <c r="S27" s="23">
+        <v>1</v>
+      </c>
+      <c r="T27" s="23">
+        <v>1</v>
+      </c>
       <c r="U27" s="26">
         <f>IF(I27=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7231,7 +7279,7 @@
       </c>
       <c r="H28" s="33">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I28" s="32">
         <v>2</v>
@@ -7257,10 +7305,18 @@
       <c r="P28" s="29">
         <v>3</v>
       </c>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
+      <c r="Q28" s="32" t="s">
+        <v>857</v>
+      </c>
+      <c r="R28" s="29" t="s">
+        <v>857</v>
+      </c>
+      <c r="S28" s="29" t="s">
+        <v>857</v>
+      </c>
+      <c r="T28" s="29" t="s">
+        <v>857</v>
+      </c>
       <c r="U28" s="32">
         <f>IF(I28=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7315,12 +7371,12 @@
         <v>8</v>
       </c>
       <c r="G29" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(Q29:T29)</f>
+        <v>3</v>
       </c>
       <c r="H29" s="27">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.95833333333333326</v>
       </c>
       <c r="I29" s="26">
         <v>2</v>
@@ -7346,10 +7402,18 @@
       <c r="P29" s="23">
         <v>3</v>
       </c>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="23"/>
-      <c r="S29" s="23"/>
-      <c r="T29" s="23"/>
+      <c r="Q29" s="26">
+        <v>0</v>
+      </c>
+      <c r="R29" s="23">
+        <v>1</v>
+      </c>
+      <c r="S29" s="23">
+        <v>1</v>
+      </c>
+      <c r="T29" s="23">
+        <v>1</v>
+      </c>
       <c r="U29" s="26">
         <f>IF(I29=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7405,11 +7469,11 @@
       </c>
       <c r="G30" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" s="33">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I30" s="32">
         <v>2</v>
@@ -7435,10 +7499,18 @@
       <c r="P30" s="29">
         <v>4</v>
       </c>
-      <c r="Q30" s="32"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
+      <c r="Q30" s="32">
+        <v>0</v>
+      </c>
+      <c r="R30" s="29">
+        <v>0</v>
+      </c>
+      <c r="S30" s="29">
+        <v>1</v>
+      </c>
+      <c r="T30" s="29">
+        <v>1</v>
+      </c>
       <c r="U30" s="32">
         <f>IF(I30=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7494,11 +7566,11 @@
       </c>
       <c r="G31" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H31" s="27">
         <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <v>0.875</v>
       </c>
       <c r="I31" s="26">
         <v>4</v>
@@ -7524,10 +7596,18 @@
       <c r="P31" s="23">
         <v>3</v>
       </c>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="23"/>
-      <c r="S31" s="23"/>
-      <c r="T31" s="23"/>
+      <c r="Q31" s="26">
+        <v>1</v>
+      </c>
+      <c r="R31" s="23">
+        <v>1</v>
+      </c>
+      <c r="S31" s="23">
+        <v>1</v>
+      </c>
+      <c r="T31" s="23">
+        <v>1</v>
+      </c>
       <c r="U31" s="26">
         <f>IF(I31=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>0</v>
@@ -7583,11 +7663,11 @@
       </c>
       <c r="G32" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32" s="33">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="I32" s="32">
         <v>2</v>
@@ -7613,10 +7693,18 @@
       <c r="P32" s="29">
         <v>3</v>
       </c>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
+      <c r="Q32" s="32">
+        <v>0</v>
+      </c>
+      <c r="R32" s="29">
+        <v>1</v>
+      </c>
+      <c r="S32" s="29">
+        <v>1</v>
+      </c>
+      <c r="T32" s="29">
+        <v>1</v>
+      </c>
       <c r="U32" s="32">
         <f>IF(I32=VLOOKUP(VALUE(I$1),Questions[#All],5,FALSE),1,0)</f>
         <v>1</v>
@@ -7676,7 +7764,7 @@
       </c>
       <c r="H33" s="27">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I33" s="26">
         <v>2</v>
@@ -7764,8 +7852,8 @@
         <v>0</v>
       </c>
       <c r="H34" s="33">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" ref="H34:H65" si="3">SUM(F34:G34)/24+0.5</f>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I34" s="32">
         <v>2</v>
@@ -7853,8 +7941,8 @@
         <v>0</v>
       </c>
       <c r="H35" s="27">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" si="3"/>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I35" s="26">
         <v>2</v>
@@ -7942,8 +8030,8 @@
         <v>0</v>
       </c>
       <c r="H36" s="33">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.75</v>
       </c>
       <c r="I36" s="32">
         <v>2</v>
@@ -8031,8 +8119,8 @@
         <v>0</v>
       </c>
       <c r="H37" s="27">
-        <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.54166666666666663</v>
       </c>
       <c r="I37" s="26">
         <v>1</v>
@@ -8120,8 +8208,8 @@
         <v>0</v>
       </c>
       <c r="H38" s="33">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I38" s="32">
         <v>1</v>
@@ -8209,8 +8297,8 @@
         <v>0</v>
       </c>
       <c r="H39" s="27">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.75</v>
       </c>
       <c r="I39" s="26">
         <v>2</v>
@@ -8298,8 +8386,8 @@
         <v>0</v>
       </c>
       <c r="H40" s="33">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="3"/>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I40" s="32">
         <v>2</v>
@@ -8387,8 +8475,8 @@
         <v>0</v>
       </c>
       <c r="H41" s="27">
-        <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.54166666666666663</v>
       </c>
       <c r="I41" s="26">
         <v>4</v>
@@ -8476,8 +8564,8 @@
         <v>0</v>
       </c>
       <c r="H42" s="33">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" si="3"/>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I42" s="32">
         <v>2</v>
@@ -8565,8 +8653,8 @@
         <v>0</v>
       </c>
       <c r="H43" s="27">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" si="3"/>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I43" s="26">
         <v>1</v>
@@ -8654,8 +8742,8 @@
         <v>0</v>
       </c>
       <c r="H44" s="33">
-        <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.54166666666666663</v>
       </c>
       <c r="I44" s="32">
         <v>1</v>
@@ -8743,8 +8831,8 @@
         <v>0</v>
       </c>
       <c r="H45" s="27">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" si="3"/>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I45" s="26">
         <v>2</v>
@@ -8832,8 +8920,8 @@
         <v>0</v>
       </c>
       <c r="H46" s="33">
-        <f t="shared" si="2"/>
-        <v>0.16666666666666666</v>
+        <f t="shared" si="3"/>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I46" s="32">
         <v>3</v>
@@ -8921,8 +9009,8 @@
         <v>0</v>
       </c>
       <c r="H47" s="27">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f t="shared" si="3"/>
+        <v>0.625</v>
       </c>
       <c r="I47" s="26">
         <v>1</v>
@@ -9006,8 +9094,8 @@
         <v>0</v>
       </c>
       <c r="H48" s="33">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <f t="shared" si="3"/>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I48" s="32">
         <v>1</v>
@@ -9095,8 +9183,8 @@
         <v>0</v>
       </c>
       <c r="H49" s="27">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f t="shared" si="3"/>
+        <v>0.625</v>
       </c>
       <c r="I49" s="26">
         <v>3</v>
@@ -9184,8 +9272,8 @@
         <v>0</v>
       </c>
       <c r="H50" s="33">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" si="3"/>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I50" s="32">
         <v>1</v>
@@ -9273,8 +9361,8 @@
         <v>0</v>
       </c>
       <c r="H51" s="27">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" si="3"/>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I51" s="26">
         <v>2</v>
@@ -9362,8 +9450,8 @@
         <v>0</v>
       </c>
       <c r="H52" s="33">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I52" s="32">
         <v>1</v>
@@ -9451,8 +9539,8 @@
         <v>0</v>
       </c>
       <c r="H53" s="27">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" si="3"/>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I53" s="26">
         <v>2</v>
@@ -9540,8 +9628,8 @@
         <v>0</v>
       </c>
       <c r="H54" s="33">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <f t="shared" si="3"/>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I54" s="32">
         <v>2</v>
@@ -9629,8 +9717,8 @@
         <v>0</v>
       </c>
       <c r="H55" s="27">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.75</v>
       </c>
       <c r="I55" s="26">
         <v>1</v>
@@ -9718,8 +9806,8 @@
         <v>0</v>
       </c>
       <c r="H56" s="33">
-        <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.54166666666666663</v>
       </c>
       <c r="I56" s="32">
         <v>3</v>
@@ -9807,8 +9895,8 @@
         <v>0</v>
       </c>
       <c r="H57" s="27">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f t="shared" si="3"/>
+        <v>0.625</v>
       </c>
       <c r="I57" s="26">
         <v>3</v>
@@ -9896,8 +9984,8 @@
         <v>0</v>
       </c>
       <c r="H58" s="33">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I58" s="32">
         <v>2</v>
@@ -9979,8 +10067,8 @@
         <v>0</v>
       </c>
       <c r="H59" s="27">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.75</v>
       </c>
       <c r="I59" s="26">
         <v>2</v>
@@ -10068,8 +10156,8 @@
         <v>0</v>
       </c>
       <c r="H60" s="33">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I60" s="32">
         <v>3</v>
@@ -10157,8 +10245,8 @@
         <v>0</v>
       </c>
       <c r="H61" s="27">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.75</v>
       </c>
       <c r="I61" s="26">
         <v>2</v>
@@ -10246,8 +10334,8 @@
         <v>0</v>
       </c>
       <c r="H62" s="33">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" si="3"/>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I62" s="32">
         <v>2</v>
@@ -10335,8 +10423,8 @@
         <v>0</v>
       </c>
       <c r="H63" s="27">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I63" s="26">
         <v>1</v>
@@ -10424,8 +10512,8 @@
         <v>0</v>
       </c>
       <c r="H64" s="33">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.75</v>
       </c>
       <c r="I64" s="32">
         <v>1</v>
@@ -10513,8 +10601,8 @@
         <v>0</v>
       </c>
       <c r="H65" s="27">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.75</v>
       </c>
       <c r="I65" s="26">
         <v>4</v>
@@ -10602,8 +10690,8 @@
         <v>0</v>
       </c>
       <c r="H66" s="33">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" ref="H66:H97" si="4">SUM(F66:G66)/24+0.5</f>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I66" s="32">
         <v>2</v>
@@ -10691,8 +10779,8 @@
         <v>0</v>
       </c>
       <c r="H67" s="27">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I67" s="26">
         <v>2</v>
@@ -10780,8 +10868,8 @@
         <v>0</v>
       </c>
       <c r="H68" s="33">
-        <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <f t="shared" si="4"/>
+        <v>0.79166666666666674</v>
       </c>
       <c r="I68" s="32">
         <v>2</v>
@@ -10869,8 +10957,8 @@
         <v>0</v>
       </c>
       <c r="H69" s="27">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="4"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I69" s="26">
         <v>4</v>
@@ -10958,8 +11046,8 @@
         <v>0</v>
       </c>
       <c r="H70" s="33">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I70" s="32">
         <v>2</v>
@@ -11047,8 +11135,8 @@
         <v>0</v>
       </c>
       <c r="H71" s="27">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I71" s="26">
         <v>2</v>
@@ -11136,8 +11224,8 @@
         <v>0</v>
       </c>
       <c r="H72" s="33">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <f t="shared" si="4"/>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I72" s="32">
         <v>2</v>
@@ -11225,8 +11313,8 @@
         <v>0</v>
       </c>
       <c r="H73" s="27">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="4"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I73" s="26">
         <v>1</v>
@@ -11314,8 +11402,8 @@
         <v>0</v>
       </c>
       <c r="H74" s="33">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I74" s="32">
         <v>2</v>
@@ -11403,8 +11491,8 @@
         <v>0</v>
       </c>
       <c r="H75" s="27">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <f t="shared" si="4"/>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I75" s="26">
         <v>2</v>
@@ -11492,8 +11580,8 @@
         <v>0</v>
       </c>
       <c r="H76" s="33">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="4"/>
+        <v>0.75</v>
       </c>
       <c r="I76" s="32">
         <v>2</v>
@@ -11581,8 +11669,8 @@
         <v>0</v>
       </c>
       <c r="H77" s="27">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <f t="shared" si="4"/>
+        <v>0.70833333333333337</v>
       </c>
       <c r="I77" s="26">
         <v>2</v>
@@ -11666,8 +11754,8 @@
         <v>0</v>
       </c>
       <c r="H78" s="33">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
+        <f t="shared" si="4"/>
+        <v>0.75</v>
       </c>
       <c r="I78" s="32">
         <v>4</v>
@@ -11755,8 +11843,8 @@
         <v>0</v>
       </c>
       <c r="H79" s="27">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f t="shared" si="4"/>
+        <v>0.625</v>
       </c>
       <c r="I79" s="26">
         <v>2</v>
@@ -11844,8 +11932,8 @@
         <v>0</v>
       </c>
       <c r="H80" s="33">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
+        <f t="shared" si="4"/>
+        <v>0.625</v>
       </c>
       <c r="I80" s="32">
         <v>2</v>
@@ -11933,8 +12021,8 @@
         <v>0</v>
       </c>
       <c r="H81" s="27">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
       </c>
       <c r="I81" s="26">
         <v>2</v>
@@ -12022,8 +12110,8 @@
         <v>0</v>
       </c>
       <c r="H82" s="39">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="4"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I82" s="38">
         <v>3</v>
@@ -12111,8 +12199,8 @@
         <v>0</v>
       </c>
       <c r="H83" s="33">
-        <f>SUM(F83:G83)/12</f>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="4"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I83" s="32">
         <v>2</v>
@@ -12177,7 +12265,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:P83">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>U2=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12190,6 +12278,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="G2:G83" formulaRange="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
